--- a/data/retail_dataset_cleaned.xlsx
+++ b/data/retail_dataset_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\retail_data_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FE2D16-6818-4984-9AA6-54E18E7AA1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21A3CC1-7ED1-4AAA-8F6A-4C4EEDEEC741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8406" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8406" uniqueCount="1039">
   <si>
     <t>retailer</t>
   </si>
@@ -895,9 +895,6 @@
     <t>RET3399</t>
   </si>
   <si>
-    <t>Direct;</t>
-  </si>
-  <si>
     <t>RET6654</t>
   </si>
   <si>
@@ -1484,9 +1481,6 @@
   </si>
   <si>
     <t>RET7790</t>
-  </si>
-  <si>
-    <t>In-store;</t>
   </si>
   <si>
     <t>RET1071</t>
@@ -3489,16 +3483,15 @@
   <dimension ref="A1:M1200"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
-    <col min="2" max="2" width="9.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="9.77734375" customWidth="1"/>
-    <col min="10" max="10" width="10.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -11701,7 +11694,7 @@
         <v>0.2571</v>
       </c>
       <c r="M200" t="s">
-        <v>291</v>
+        <v>54</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.3">
@@ -11709,7 +11702,7 @@
         <v>104</v>
       </c>
       <c r="B201" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C201" s="1">
         <v>45441</v>
@@ -11750,7 +11743,7 @@
         <v>63</v>
       </c>
       <c r="B202" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C202" s="1">
         <v>45843</v>
@@ -11791,7 +11784,7 @@
         <v>71</v>
       </c>
       <c r="B203" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C203" s="1">
         <v>45977</v>
@@ -11832,7 +11825,7 @@
         <v>79</v>
       </c>
       <c r="B204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C204" s="1">
         <v>45297</v>
@@ -11873,7 +11866,7 @@
         <v>52</v>
       </c>
       <c r="B205" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C205" s="1">
         <v>45953</v>
@@ -11914,7 +11907,7 @@
         <v>55</v>
       </c>
       <c r="B206" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C206" s="1">
         <v>45472</v>
@@ -11955,7 +11948,7 @@
         <v>32</v>
       </c>
       <c r="B207" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C207" s="1">
         <v>45597</v>
@@ -11996,7 +11989,7 @@
         <v>43</v>
       </c>
       <c r="B208" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C208" s="1">
         <v>45771</v>
@@ -12037,7 +12030,7 @@
         <v>55</v>
       </c>
       <c r="B209" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C209" s="1">
         <v>45637</v>
@@ -12078,7 +12071,7 @@
         <v>129</v>
       </c>
       <c r="B210" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C210" s="1">
         <v>45627</v>
@@ -12160,7 +12153,7 @@
         <v>123</v>
       </c>
       <c r="B212" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C212" s="1">
         <v>45961</v>
@@ -12201,7 +12194,7 @@
         <v>26</v>
       </c>
       <c r="B213" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C213" s="1">
         <v>45946</v>
@@ -12242,7 +12235,7 @@
         <v>84</v>
       </c>
       <c r="B214" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C214" s="1">
         <v>46010</v>
@@ -12283,7 +12276,7 @@
         <v>37</v>
       </c>
       <c r="B215" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C215" s="1">
         <v>45749</v>
@@ -12324,7 +12317,7 @@
         <v>63</v>
       </c>
       <c r="B216" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C216" s="1">
         <v>45445</v>
@@ -12365,7 +12358,7 @@
         <v>142</v>
       </c>
       <c r="B217" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C217" s="1">
         <v>45814</v>
@@ -12406,7 +12399,7 @@
         <v>60</v>
       </c>
       <c r="B218" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C218" s="1">
         <v>45314</v>
@@ -12447,7 +12440,7 @@
         <v>84</v>
       </c>
       <c r="B219" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C219" s="1">
         <v>45846</v>
@@ -12488,7 +12481,7 @@
         <v>84</v>
       </c>
       <c r="B220" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C220" s="1">
         <v>45751</v>
@@ -12529,7 +12522,7 @@
         <v>104</v>
       </c>
       <c r="B221" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C221" s="1">
         <v>45422</v>
@@ -12570,7 +12563,7 @@
         <v>129</v>
       </c>
       <c r="B222" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C222" s="1">
         <v>45680</v>
@@ -12611,7 +12604,7 @@
         <v>32</v>
       </c>
       <c r="B223" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C223" s="1">
         <v>45921</v>
@@ -12652,7 +12645,7 @@
         <v>71</v>
       </c>
       <c r="B224" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C224" s="1">
         <v>45703</v>
@@ -12693,7 +12686,7 @@
         <v>26</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C225" s="1">
         <v>45881</v>
@@ -12734,7 +12727,7 @@
         <v>71</v>
       </c>
       <c r="B226" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C226" s="1">
         <v>45599</v>
@@ -12775,7 +12768,7 @@
         <v>142</v>
       </c>
       <c r="B227" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C227" s="1">
         <v>45644</v>
@@ -12816,7 +12809,7 @@
         <v>142</v>
       </c>
       <c r="B228" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C228" s="1">
         <v>45522</v>
@@ -12857,7 +12850,7 @@
         <v>43</v>
       </c>
       <c r="B229" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C229" s="1">
         <v>45540</v>
@@ -12898,7 +12891,7 @@
         <v>63</v>
       </c>
       <c r="B230" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C230" s="1">
         <v>45566</v>
@@ -12939,7 +12932,7 @@
         <v>63</v>
       </c>
       <c r="B231" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C231" s="1">
         <v>45505</v>
@@ -12980,7 +12973,7 @@
         <v>71</v>
       </c>
       <c r="B232" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C232" s="1">
         <v>45698</v>
@@ -13021,7 +13014,7 @@
         <v>13</v>
       </c>
       <c r="B233" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C233" s="1">
         <v>45817</v>
@@ -13062,7 +13055,7 @@
         <v>52</v>
       </c>
       <c r="B234" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C234" s="1">
         <v>45338</v>
@@ -13103,7 +13096,7 @@
         <v>129</v>
       </c>
       <c r="B235" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C235" s="1">
         <v>45448</v>
@@ -13144,7 +13137,7 @@
         <v>13</v>
       </c>
       <c r="B236" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C236" s="1">
         <v>45949</v>
@@ -13185,7 +13178,7 @@
         <v>32</v>
       </c>
       <c r="B237" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C237" s="1">
         <v>45326</v>
@@ -13226,7 +13219,7 @@
         <v>43</v>
       </c>
       <c r="B238" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C238" s="1">
         <v>45515</v>
@@ -13267,7 +13260,7 @@
         <v>142</v>
       </c>
       <c r="B239" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C239" s="1">
         <v>45298</v>
@@ -13308,7 +13301,7 @@
         <v>123</v>
       </c>
       <c r="B240" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C240" s="1">
         <v>46006</v>
@@ -13349,7 +13342,7 @@
         <v>13</v>
       </c>
       <c r="B241" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C241" s="1">
         <v>45565</v>
@@ -13390,7 +13383,7 @@
         <v>26</v>
       </c>
       <c r="B242" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C242" s="1">
         <v>45961</v>
@@ -13431,7 +13424,7 @@
         <v>55</v>
       </c>
       <c r="B243" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C243" s="1">
         <v>45803</v>
@@ -13472,7 +13465,7 @@
         <v>142</v>
       </c>
       <c r="B244" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C244" s="1">
         <v>45339</v>
@@ -13513,7 +13506,7 @@
         <v>123</v>
       </c>
       <c r="B245" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C245" s="1">
         <v>45893</v>
@@ -13554,7 +13547,7 @@
         <v>52</v>
       </c>
       <c r="B246" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C246" s="1">
         <v>45435</v>
@@ -13595,7 +13588,7 @@
         <v>52</v>
       </c>
       <c r="B247" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C247" s="1">
         <v>45626</v>
@@ -13636,7 +13629,7 @@
         <v>129</v>
       </c>
       <c r="B248" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C248" s="1">
         <v>45988</v>
@@ -13677,7 +13670,7 @@
         <v>13</v>
       </c>
       <c r="B249" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C249" s="1">
         <v>45681</v>
@@ -13718,7 +13711,7 @@
         <v>84</v>
       </c>
       <c r="B250" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C250" s="1">
         <v>45396</v>
@@ -13759,7 +13752,7 @@
         <v>123</v>
       </c>
       <c r="B251" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C251" s="1">
         <v>45654</v>
@@ -13800,7 +13793,7 @@
         <v>129</v>
       </c>
       <c r="B252" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C252" s="1">
         <v>45378</v>
@@ -13841,7 +13834,7 @@
         <v>26</v>
       </c>
       <c r="B253" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C253" s="1">
         <v>45796</v>
@@ -13882,7 +13875,7 @@
         <v>84</v>
       </c>
       <c r="B254" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C254" s="1">
         <v>45544</v>
@@ -13923,7 +13916,7 @@
         <v>52</v>
       </c>
       <c r="B255" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C255" s="1">
         <v>45629</v>
@@ -13964,7 +13957,7 @@
         <v>142</v>
       </c>
       <c r="B256" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C256" s="1">
         <v>45473</v>
@@ -14005,7 +13998,7 @@
         <v>13</v>
       </c>
       <c r="B257" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C257" s="1">
         <v>45665</v>
@@ -14046,7 +14039,7 @@
         <v>123</v>
       </c>
       <c r="B258" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C258" s="1">
         <v>46017</v>
@@ -14087,7 +14080,7 @@
         <v>142</v>
       </c>
       <c r="B259" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C259" s="1">
         <v>45940</v>
@@ -14128,7 +14121,7 @@
         <v>142</v>
       </c>
       <c r="B260" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C260" s="1">
         <v>45839</v>
@@ -14169,7 +14162,7 @@
         <v>37</v>
       </c>
       <c r="B261" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C261" s="1">
         <v>45546</v>
@@ -14210,7 +14203,7 @@
         <v>52</v>
       </c>
       <c r="B262" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C262" s="1">
         <v>45400</v>
@@ -14251,7 +14244,7 @@
         <v>71</v>
       </c>
       <c r="B263" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C263" s="1">
         <v>45675</v>
@@ -14292,7 +14285,7 @@
         <v>142</v>
       </c>
       <c r="B264" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C264" s="1">
         <v>45594</v>
@@ -14333,7 +14326,7 @@
         <v>142</v>
       </c>
       <c r="B265" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C265" s="1">
         <v>45779</v>
@@ -14374,7 +14367,7 @@
         <v>123</v>
       </c>
       <c r="B266" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C266" s="1">
         <v>45955</v>
@@ -14415,7 +14408,7 @@
         <v>129</v>
       </c>
       <c r="B267" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C267" s="1">
         <v>45529</v>
@@ -14456,7 +14449,7 @@
         <v>60</v>
       </c>
       <c r="B268" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C268" s="1">
         <v>45690</v>
@@ -14497,7 +14490,7 @@
         <v>79</v>
       </c>
       <c r="B269" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C269" s="1">
         <v>45483</v>
@@ -14538,7 +14531,7 @@
         <v>52</v>
       </c>
       <c r="B270" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C270" s="1">
         <v>45917</v>
@@ -14579,7 +14572,7 @@
         <v>37</v>
       </c>
       <c r="B271" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C271" s="1">
         <v>45612</v>
@@ -14620,7 +14613,7 @@
         <v>129</v>
       </c>
       <c r="B272" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C272" s="1">
         <v>45880</v>
@@ -14661,7 +14654,7 @@
         <v>55</v>
       </c>
       <c r="B273" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C273" s="1">
         <v>45587</v>
@@ -14702,7 +14695,7 @@
         <v>142</v>
       </c>
       <c r="B274" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C274" s="1">
         <v>45491</v>
@@ -14743,7 +14736,7 @@
         <v>142</v>
       </c>
       <c r="B275" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C275" s="1">
         <v>45376</v>
@@ -14784,7 +14777,7 @@
         <v>55</v>
       </c>
       <c r="B276" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C276" s="1">
         <v>45871</v>
@@ -14825,7 +14818,7 @@
         <v>32</v>
       </c>
       <c r="B277" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C277" s="1">
         <v>45851</v>
@@ -14866,7 +14859,7 @@
         <v>37</v>
       </c>
       <c r="B278" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C278" s="1">
         <v>45412</v>
@@ -14907,7 +14900,7 @@
         <v>55</v>
       </c>
       <c r="B279" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C279" s="1">
         <v>45503</v>
@@ -14948,7 +14941,7 @@
         <v>26</v>
       </c>
       <c r="B280" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C280" s="1">
         <v>45878</v>
@@ -14989,7 +14982,7 @@
         <v>13</v>
       </c>
       <c r="B281" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C281" s="1">
         <v>46010</v>
@@ -15030,7 +15023,7 @@
         <v>142</v>
       </c>
       <c r="B282" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C282" s="1">
         <v>45883</v>
@@ -15071,7 +15064,7 @@
         <v>104</v>
       </c>
       <c r="B283" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C283" s="1">
         <v>45576</v>
@@ -15112,7 +15105,7 @@
         <v>60</v>
       </c>
       <c r="B284" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C284" s="1">
         <v>45356</v>
@@ -15153,7 +15146,7 @@
         <v>52</v>
       </c>
       <c r="B285" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C285" s="1">
         <v>45883</v>
@@ -15194,7 +15187,7 @@
         <v>32</v>
       </c>
       <c r="B286" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C286" s="1">
         <v>45933</v>
@@ -15235,7 +15228,7 @@
         <v>63</v>
       </c>
       <c r="B287" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C287" s="1">
         <v>45957</v>
@@ -15276,7 +15269,7 @@
         <v>55</v>
       </c>
       <c r="B288" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C288" s="1">
         <v>45697</v>
@@ -15317,7 +15310,7 @@
         <v>43</v>
       </c>
       <c r="B289" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C289" s="1">
         <v>45823</v>
@@ -15358,7 +15351,7 @@
         <v>142</v>
       </c>
       <c r="B290" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C290" s="1">
         <v>45526</v>
@@ -15399,7 +15392,7 @@
         <v>104</v>
       </c>
       <c r="B291" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C291" s="1">
         <v>45948</v>
@@ -15440,7 +15433,7 @@
         <v>63</v>
       </c>
       <c r="B292" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C292" s="1">
         <v>45713</v>
@@ -15481,7 +15474,7 @@
         <v>104</v>
       </c>
       <c r="B293" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C293" s="1">
         <v>45731</v>
@@ -15522,7 +15515,7 @@
         <v>26</v>
       </c>
       <c r="B294" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C294" s="1">
         <v>45966</v>
@@ -15563,7 +15556,7 @@
         <v>71</v>
       </c>
       <c r="B295" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C295" s="1">
         <v>45687</v>
@@ -15604,7 +15597,7 @@
         <v>52</v>
       </c>
       <c r="B296" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C296" s="1">
         <v>45688</v>
@@ -15645,7 +15638,7 @@
         <v>123</v>
       </c>
       <c r="B297" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C297" s="1">
         <v>45306</v>
@@ -15686,7 +15679,7 @@
         <v>129</v>
       </c>
       <c r="B298" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C298" s="1">
         <v>46010</v>
@@ -15727,7 +15720,7 @@
         <v>37</v>
       </c>
       <c r="B299" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C299" s="1">
         <v>45500</v>
@@ -15768,7 +15761,7 @@
         <v>26</v>
       </c>
       <c r="B300" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C300" s="1">
         <v>45536</v>
@@ -15809,7 +15802,7 @@
         <v>55</v>
       </c>
       <c r="B301" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C301" s="1">
         <v>45304</v>
@@ -15850,7 +15843,7 @@
         <v>55</v>
       </c>
       <c r="B302" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C302" s="1">
         <v>45421</v>
@@ -15891,7 +15884,7 @@
         <v>13</v>
       </c>
       <c r="B303" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C303" s="1">
         <v>45800</v>
@@ -15932,7 +15925,7 @@
         <v>13</v>
       </c>
       <c r="B304" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C304" s="1">
         <v>45879</v>
@@ -15973,7 +15966,7 @@
         <v>32</v>
       </c>
       <c r="B305" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C305" s="1">
         <v>45664</v>
@@ -16014,7 +16007,7 @@
         <v>71</v>
       </c>
       <c r="B306" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C306" s="1">
         <v>45546</v>
@@ -16055,7 +16048,7 @@
         <v>55</v>
       </c>
       <c r="B307" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C307" s="1">
         <v>45820</v>
@@ -16096,7 +16089,7 @@
         <v>37</v>
       </c>
       <c r="B308" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C308" s="1">
         <v>45300</v>
@@ -16137,7 +16130,7 @@
         <v>84</v>
       </c>
       <c r="B309" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C309" s="1">
         <v>45492</v>
@@ -16178,7 +16171,7 @@
         <v>123</v>
       </c>
       <c r="B310" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C310" s="1">
         <v>45293</v>
@@ -16219,7 +16212,7 @@
         <v>43</v>
       </c>
       <c r="B311" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C311" s="1">
         <v>45387</v>
@@ -16260,7 +16253,7 @@
         <v>79</v>
       </c>
       <c r="B312" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C312" s="1">
         <v>45428</v>
@@ -16301,7 +16294,7 @@
         <v>26</v>
       </c>
       <c r="B313" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C313" s="1">
         <v>45614</v>
@@ -16342,7 +16335,7 @@
         <v>79</v>
       </c>
       <c r="B314" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C314" s="1">
         <v>45400</v>
@@ -16383,7 +16376,7 @@
         <v>60</v>
       </c>
       <c r="B315" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C315" s="1">
         <v>45766</v>
@@ -16424,7 +16417,7 @@
         <v>32</v>
       </c>
       <c r="B316" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C316" s="1">
         <v>45627</v>
@@ -16465,7 +16458,7 @@
         <v>13</v>
       </c>
       <c r="B317" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C317" s="1">
         <v>45323</v>
@@ -16506,7 +16499,7 @@
         <v>79</v>
       </c>
       <c r="B318" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C318" s="1">
         <v>45355</v>
@@ -16547,7 +16540,7 @@
         <v>13</v>
       </c>
       <c r="B319" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C319" s="1">
         <v>45314</v>
@@ -16588,7 +16581,7 @@
         <v>79</v>
       </c>
       <c r="B320" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C320" s="1">
         <v>45764</v>
@@ -16629,7 +16622,7 @@
         <v>129</v>
       </c>
       <c r="B321" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C321" s="1">
         <v>45654</v>
@@ -16711,7 +16704,7 @@
         <v>71</v>
       </c>
       <c r="B323" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C323" s="1">
         <v>45311</v>
@@ -16752,7 +16745,7 @@
         <v>52</v>
       </c>
       <c r="B324" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C324" s="1">
         <v>45568</v>
@@ -16793,7 +16786,7 @@
         <v>32</v>
       </c>
       <c r="B325" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C325" s="1">
         <v>45834</v>
@@ -16834,7 +16827,7 @@
         <v>32</v>
       </c>
       <c r="B326" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C326" s="1">
         <v>45881</v>
@@ -16875,7 +16868,7 @@
         <v>123</v>
       </c>
       <c r="B327" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C327" s="1">
         <v>45873</v>
@@ -16916,7 +16909,7 @@
         <v>26</v>
       </c>
       <c r="B328" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C328" s="1">
         <v>45794</v>
@@ -16957,7 +16950,7 @@
         <v>52</v>
       </c>
       <c r="B329" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C329" s="1">
         <v>45425</v>
@@ -16998,7 +16991,7 @@
         <v>79</v>
       </c>
       <c r="B330" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C330" s="1">
         <v>45665</v>
@@ -17039,7 +17032,7 @@
         <v>55</v>
       </c>
       <c r="B331" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C331" s="1">
         <v>45946</v>
@@ -17080,7 +17073,7 @@
         <v>71</v>
       </c>
       <c r="B332" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C332" s="1">
         <v>45679</v>
@@ -17121,7 +17114,7 @@
         <v>104</v>
       </c>
       <c r="B333" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C333" s="1">
         <v>45478</v>
@@ -17162,7 +17155,7 @@
         <v>43</v>
       </c>
       <c r="B334" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C334" s="1">
         <v>45371</v>
@@ -17203,7 +17196,7 @@
         <v>60</v>
       </c>
       <c r="B335" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C335" s="1">
         <v>45563</v>
@@ -17244,7 +17237,7 @@
         <v>32</v>
       </c>
       <c r="B336" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C336" s="1">
         <v>45740</v>
@@ -17285,7 +17278,7 @@
         <v>142</v>
       </c>
       <c r="B337" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C337" s="1">
         <v>45458</v>
@@ -17326,7 +17319,7 @@
         <v>37</v>
       </c>
       <c r="B338" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C338" s="1">
         <v>45466</v>
@@ -17367,7 +17360,7 @@
         <v>142</v>
       </c>
       <c r="B339" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C339" s="1">
         <v>45733</v>
@@ -17408,7 +17401,7 @@
         <v>129</v>
       </c>
       <c r="B340" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C340" s="1">
         <v>45563</v>
@@ -17449,7 +17442,7 @@
         <v>43</v>
       </c>
       <c r="B341" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C341" s="1">
         <v>45661</v>
@@ -17490,7 +17483,7 @@
         <v>79</v>
       </c>
       <c r="B342" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C342" s="1">
         <v>45503</v>
@@ -17531,7 +17524,7 @@
         <v>142</v>
       </c>
       <c r="B343" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C343" s="1">
         <v>45385</v>
@@ -17572,7 +17565,7 @@
         <v>13</v>
       </c>
       <c r="B344" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C344" s="1">
         <v>45768</v>
@@ -17613,7 +17606,7 @@
         <v>37</v>
       </c>
       <c r="B345" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C345" s="1">
         <v>45846</v>
@@ -17654,7 +17647,7 @@
         <v>142</v>
       </c>
       <c r="B346" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C346" s="1">
         <v>45779</v>
@@ -17695,7 +17688,7 @@
         <v>43</v>
       </c>
       <c r="B347" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C347" s="1">
         <v>45751</v>
@@ -17736,7 +17729,7 @@
         <v>63</v>
       </c>
       <c r="B348" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C348" s="1">
         <v>45901</v>
@@ -17777,7 +17770,7 @@
         <v>13</v>
       </c>
       <c r="B349" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C349" s="1">
         <v>45761</v>
@@ -17818,7 +17811,7 @@
         <v>79</v>
       </c>
       <c r="B350" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C350" s="1">
         <v>45868</v>
@@ -17859,7 +17852,7 @@
         <v>142</v>
       </c>
       <c r="B351" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C351" s="1">
         <v>45330</v>
@@ -17900,7 +17893,7 @@
         <v>104</v>
       </c>
       <c r="B352" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C352" s="1">
         <v>45999</v>
@@ -17941,7 +17934,7 @@
         <v>26</v>
       </c>
       <c r="B353" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C353" s="1">
         <v>45579</v>
@@ -17982,7 +17975,7 @@
         <v>13</v>
       </c>
       <c r="B354" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C354" s="1">
         <v>45911</v>
@@ -18023,7 +18016,7 @@
         <v>84</v>
       </c>
       <c r="B355" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C355" s="1">
         <v>45819</v>
@@ -18064,7 +18057,7 @@
         <v>123</v>
       </c>
       <c r="B356" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C356" s="1">
         <v>45489</v>
@@ -18105,7 +18098,7 @@
         <v>13</v>
       </c>
       <c r="B357" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C357" s="1">
         <v>45767</v>
@@ -18146,7 +18139,7 @@
         <v>60</v>
       </c>
       <c r="B358" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C358" s="1">
         <v>45777</v>
@@ -18187,7 +18180,7 @@
         <v>26</v>
       </c>
       <c r="B359" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C359" s="1">
         <v>45687</v>
@@ -18228,7 +18221,7 @@
         <v>63</v>
       </c>
       <c r="B360" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C360" s="1">
         <v>45959</v>
@@ -18269,7 +18262,7 @@
         <v>123</v>
       </c>
       <c r="B361" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C361" s="1">
         <v>45550</v>
@@ -18310,7 +18303,7 @@
         <v>13</v>
       </c>
       <c r="B362" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C362" s="1">
         <v>45769</v>
@@ -18351,7 +18344,7 @@
         <v>26</v>
       </c>
       <c r="B363" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C363" s="1">
         <v>45992</v>
@@ -18392,7 +18385,7 @@
         <v>13</v>
       </c>
       <c r="B364" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C364" s="1">
         <v>45484</v>
@@ -18433,7 +18426,7 @@
         <v>104</v>
       </c>
       <c r="B365" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C365" s="1">
         <v>45989</v>
@@ -18474,7 +18467,7 @@
         <v>104</v>
       </c>
       <c r="B366" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C366" s="1">
         <v>45889</v>
@@ -18515,7 +18508,7 @@
         <v>26</v>
       </c>
       <c r="B367" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C367" s="1">
         <v>45965</v>
@@ -18556,7 +18549,7 @@
         <v>55</v>
       </c>
       <c r="B368" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C368" s="1">
         <v>45962</v>
@@ -18597,7 +18590,7 @@
         <v>84</v>
       </c>
       <c r="B369" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C369" s="1">
         <v>45891</v>
@@ -18638,7 +18631,7 @@
         <v>37</v>
       </c>
       <c r="B370" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C370" s="1">
         <v>45491</v>
@@ -18679,7 +18672,7 @@
         <v>43</v>
       </c>
       <c r="B371" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C371" s="1">
         <v>45642</v>
@@ -18720,7 +18713,7 @@
         <v>142</v>
       </c>
       <c r="B372" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C372" s="1">
         <v>45938</v>
@@ -18761,7 +18754,7 @@
         <v>55</v>
       </c>
       <c r="B373" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C373" s="1">
         <v>45382</v>
@@ -18802,7 +18795,7 @@
         <v>32</v>
       </c>
       <c r="B374" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C374" s="1">
         <v>45496</v>
@@ -18843,7 +18836,7 @@
         <v>71</v>
       </c>
       <c r="B375" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C375" s="1">
         <v>45611</v>
@@ -18884,7 +18877,7 @@
         <v>26</v>
       </c>
       <c r="B376" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C376" s="1">
         <v>45758</v>
@@ -18925,7 +18918,7 @@
         <v>142</v>
       </c>
       <c r="B377" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C377" s="1">
         <v>45484</v>
@@ -18966,7 +18959,7 @@
         <v>55</v>
       </c>
       <c r="B378" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C378" s="1">
         <v>45667</v>
@@ -19007,7 +19000,7 @@
         <v>79</v>
       </c>
       <c r="B379" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C379" s="1">
         <v>45341</v>
@@ -19089,7 +19082,7 @@
         <v>79</v>
       </c>
       <c r="B381" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C381" s="1">
         <v>45924</v>
@@ -19130,7 +19123,7 @@
         <v>63</v>
       </c>
       <c r="B382" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C382" s="1">
         <v>46012</v>
@@ -19171,7 +19164,7 @@
         <v>52</v>
       </c>
       <c r="B383" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C383" s="1">
         <v>45294</v>
@@ -19212,7 +19205,7 @@
         <v>37</v>
       </c>
       <c r="B384" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C384" s="1">
         <v>45554</v>
@@ -19253,7 +19246,7 @@
         <v>26</v>
       </c>
       <c r="B385" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C385" s="1">
         <v>45985</v>
@@ -19294,7 +19287,7 @@
         <v>43</v>
       </c>
       <c r="B386" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C386" s="1">
         <v>45628</v>
@@ -19335,7 +19328,7 @@
         <v>55</v>
       </c>
       <c r="B387" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C387" s="1">
         <v>45702</v>
@@ -19376,7 +19369,7 @@
         <v>79</v>
       </c>
       <c r="B388" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C388" s="1">
         <v>46004</v>
@@ -19417,7 +19410,7 @@
         <v>55</v>
       </c>
       <c r="B389" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C389" s="1">
         <v>45659</v>
@@ -19458,7 +19451,7 @@
         <v>60</v>
       </c>
       <c r="B390" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C390" s="1">
         <v>45356</v>
@@ -19499,7 +19492,7 @@
         <v>52</v>
       </c>
       <c r="B391" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C391" s="1">
         <v>45827</v>
@@ -19540,7 +19533,7 @@
         <v>43</v>
       </c>
       <c r="B392" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C392" s="1">
         <v>45303</v>
@@ -19581,7 +19574,7 @@
         <v>52</v>
       </c>
       <c r="B393" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C393" s="1">
         <v>45630</v>
@@ -19622,7 +19615,7 @@
         <v>37</v>
       </c>
       <c r="B394" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C394" s="1">
         <v>45746</v>
@@ -19663,7 +19656,7 @@
         <v>79</v>
       </c>
       <c r="B395" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C395" s="1">
         <v>45714</v>
@@ -19704,7 +19697,7 @@
         <v>26</v>
       </c>
       <c r="B396" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C396" s="1">
         <v>45867</v>
@@ -19745,7 +19738,7 @@
         <v>52</v>
       </c>
       <c r="B397" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C397" s="1">
         <v>45964</v>
@@ -19786,7 +19779,7 @@
         <v>26</v>
       </c>
       <c r="B398" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C398" s="1">
         <v>45826</v>
@@ -19827,7 +19820,7 @@
         <v>79</v>
       </c>
       <c r="B399" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C399" s="1">
         <v>45917</v>
@@ -19868,7 +19861,7 @@
         <v>79</v>
       </c>
       <c r="B400" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C400" s="1">
         <v>45339</v>
@@ -19901,7 +19894,7 @@
         <v>0.3382</v>
       </c>
       <c r="M400" t="s">
-        <v>488</v>
+        <v>51</v>
       </c>
     </row>
     <row r="401" spans="1:13" x14ac:dyDescent="0.3">
@@ -19909,7 +19902,7 @@
         <v>142</v>
       </c>
       <c r="B401" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C401" s="1">
         <v>45835</v>
@@ -19950,7 +19943,7 @@
         <v>55</v>
       </c>
       <c r="B402" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C402" s="1">
         <v>45398</v>
@@ -19991,7 +19984,7 @@
         <v>71</v>
       </c>
       <c r="B403" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C403" s="1">
         <v>45699</v>
@@ -20032,7 +20025,7 @@
         <v>26</v>
       </c>
       <c r="B404" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C404" s="1">
         <v>45613</v>
@@ -20073,7 +20066,7 @@
         <v>55</v>
       </c>
       <c r="B405" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C405" s="1">
         <v>45847</v>
@@ -20114,7 +20107,7 @@
         <v>26</v>
       </c>
       <c r="B406" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C406" s="1">
         <v>45305</v>
@@ -20155,7 +20148,7 @@
         <v>55</v>
       </c>
       <c r="B407" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C407" s="1">
         <v>45991</v>
@@ -20196,7 +20189,7 @@
         <v>32</v>
       </c>
       <c r="B408" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C408" s="1">
         <v>45755</v>
@@ -20237,7 +20230,7 @@
         <v>71</v>
       </c>
       <c r="B409" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C409" s="1">
         <v>46004</v>
@@ -20278,7 +20271,7 @@
         <v>32</v>
       </c>
       <c r="B410" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C410" s="1">
         <v>45549</v>
@@ -20319,7 +20312,7 @@
         <v>63</v>
       </c>
       <c r="B411" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C411" s="1">
         <v>45593</v>
@@ -20360,7 +20353,7 @@
         <v>104</v>
       </c>
       <c r="B412" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C412" s="1">
         <v>45730</v>
@@ -20442,7 +20435,7 @@
         <v>142</v>
       </c>
       <c r="B414" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C414" s="1">
         <v>45366</v>
@@ -20483,7 +20476,7 @@
         <v>104</v>
       </c>
       <c r="B415" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C415" s="1">
         <v>45649</v>
@@ -20524,7 +20517,7 @@
         <v>142</v>
       </c>
       <c r="B416" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C416" s="1">
         <v>45409</v>
@@ -20565,7 +20558,7 @@
         <v>104</v>
       </c>
       <c r="B417" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C417" s="1">
         <v>45687</v>
@@ -20606,7 +20599,7 @@
         <v>60</v>
       </c>
       <c r="B418" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C418" s="1">
         <v>45336</v>
@@ -20647,7 +20640,7 @@
         <v>123</v>
       </c>
       <c r="B419" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C419" s="1">
         <v>45507</v>
@@ -20688,7 +20681,7 @@
         <v>37</v>
       </c>
       <c r="B420" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C420" s="1">
         <v>45316</v>
@@ -20729,7 +20722,7 @@
         <v>37</v>
       </c>
       <c r="B421" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C421" s="1">
         <v>45556</v>
@@ -20770,7 +20763,7 @@
         <v>123</v>
       </c>
       <c r="B422" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C422" s="1">
         <v>45891</v>
@@ -20811,7 +20804,7 @@
         <v>37</v>
       </c>
       <c r="B423" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C423" s="1">
         <v>45740</v>
@@ -20852,7 +20845,7 @@
         <v>26</v>
       </c>
       <c r="B424" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C424" s="1">
         <v>45597</v>
@@ -20893,7 +20886,7 @@
         <v>104</v>
       </c>
       <c r="B425" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C425" s="1">
         <v>45852</v>
@@ -20934,7 +20927,7 @@
         <v>43</v>
       </c>
       <c r="B426" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C426" s="1">
         <v>45480</v>
@@ -20975,7 +20968,7 @@
         <v>32</v>
       </c>
       <c r="B427" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C427" s="1">
         <v>45764</v>
@@ -21016,7 +21009,7 @@
         <v>52</v>
       </c>
       <c r="B428" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C428" s="1">
         <v>45423</v>
@@ -21057,7 +21050,7 @@
         <v>52</v>
       </c>
       <c r="B429" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C429" s="1">
         <v>46002</v>
@@ -21098,7 +21091,7 @@
         <v>123</v>
       </c>
       <c r="B430" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C430" s="1">
         <v>45544</v>
@@ -21139,7 +21132,7 @@
         <v>60</v>
       </c>
       <c r="B431" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C431" s="1">
         <v>45659</v>
@@ -21180,7 +21173,7 @@
         <v>43</v>
       </c>
       <c r="B432" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C432" s="1">
         <v>45493</v>
@@ -21221,7 +21214,7 @@
         <v>104</v>
       </c>
       <c r="B433" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C433" s="1">
         <v>45329</v>
@@ -21262,7 +21255,7 @@
         <v>71</v>
       </c>
       <c r="B434" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C434" s="1">
         <v>45429</v>
@@ -21303,7 +21296,7 @@
         <v>55</v>
       </c>
       <c r="B435" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C435" s="1">
         <v>45435</v>
@@ -21344,7 +21337,7 @@
         <v>142</v>
       </c>
       <c r="B436" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C436" s="1">
         <v>45333</v>
@@ -21385,7 +21378,7 @@
         <v>84</v>
       </c>
       <c r="B437" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C437" s="1">
         <v>45772</v>
@@ -21426,7 +21419,7 @@
         <v>13</v>
       </c>
       <c r="B438" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C438" s="1">
         <v>45875</v>
@@ -21467,7 +21460,7 @@
         <v>13</v>
       </c>
       <c r="B439" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C439" s="1">
         <v>45520</v>
@@ -21508,7 +21501,7 @@
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C440" s="1">
         <v>45461</v>
@@ -21549,7 +21542,7 @@
         <v>79</v>
       </c>
       <c r="B441" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C441" s="1">
         <v>45716</v>
@@ -21590,7 +21583,7 @@
         <v>123</v>
       </c>
       <c r="B442" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C442" s="1">
         <v>45336</v>
@@ -21631,7 +21624,7 @@
         <v>43</v>
       </c>
       <c r="B443" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C443" s="1">
         <v>45462</v>
@@ -21672,7 +21665,7 @@
         <v>37</v>
       </c>
       <c r="B444" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C444" s="1">
         <v>45751</v>
@@ -21713,7 +21706,7 @@
         <v>55</v>
       </c>
       <c r="B445" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C445" s="1">
         <v>45562</v>
@@ -21754,7 +21747,7 @@
         <v>79</v>
       </c>
       <c r="B446" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C446" s="1">
         <v>45499</v>
@@ -21795,7 +21788,7 @@
         <v>32</v>
       </c>
       <c r="B447" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C447" s="1">
         <v>45807</v>
@@ -21836,7 +21829,7 @@
         <v>129</v>
       </c>
       <c r="B448" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C448" s="1">
         <v>45336</v>
@@ -21877,7 +21870,7 @@
         <v>79</v>
       </c>
       <c r="B449" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C449" s="1">
         <v>45429</v>
@@ -21918,7 +21911,7 @@
         <v>129</v>
       </c>
       <c r="B450" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C450" s="1">
         <v>45485</v>
@@ -21959,7 +21952,7 @@
         <v>52</v>
       </c>
       <c r="B451" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C451" s="1">
         <v>45662</v>
@@ -22000,7 +21993,7 @@
         <v>84</v>
       </c>
       <c r="B452" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C452" s="1">
         <v>45988</v>
@@ -22041,7 +22034,7 @@
         <v>142</v>
       </c>
       <c r="B453" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C453" s="1">
         <v>45606</v>
@@ -22082,7 +22075,7 @@
         <v>71</v>
       </c>
       <c r="B454" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C454" s="1">
         <v>46008</v>
@@ -22123,7 +22116,7 @@
         <v>32</v>
       </c>
       <c r="B455" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C455" s="1">
         <v>45690</v>
@@ -22164,7 +22157,7 @@
         <v>13</v>
       </c>
       <c r="B456" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C456" s="1">
         <v>45671</v>
@@ -22205,7 +22198,7 @@
         <v>26</v>
       </c>
       <c r="B457" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C457" s="1">
         <v>45471</v>
@@ -22246,7 +22239,7 @@
         <v>63</v>
       </c>
       <c r="B458" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C458" s="1">
         <v>45905</v>
@@ -22287,7 +22280,7 @@
         <v>123</v>
       </c>
       <c r="B459" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C459" s="1">
         <v>45380</v>
@@ -22328,7 +22321,7 @@
         <v>37</v>
       </c>
       <c r="B460" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C460" s="1">
         <v>45864</v>
@@ -22369,7 +22362,7 @@
         <v>123</v>
       </c>
       <c r="B461" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C461" s="1">
         <v>45471</v>
@@ -22410,7 +22403,7 @@
         <v>13</v>
       </c>
       <c r="B462" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C462" s="1">
         <v>45880</v>
@@ -22451,7 +22444,7 @@
         <v>60</v>
       </c>
       <c r="B463" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C463" s="1">
         <v>45785</v>
@@ -22492,7 +22485,7 @@
         <v>52</v>
       </c>
       <c r="B464" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C464" s="1">
         <v>45653</v>
@@ -22533,7 +22526,7 @@
         <v>37</v>
       </c>
       <c r="B465" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C465" s="1">
         <v>45779</v>
@@ -22574,7 +22567,7 @@
         <v>142</v>
       </c>
       <c r="B466" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C466" s="1">
         <v>45532</v>
@@ -22615,7 +22608,7 @@
         <v>43</v>
       </c>
       <c r="B467" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C467" s="1">
         <v>45414</v>
@@ -22656,7 +22649,7 @@
         <v>84</v>
       </c>
       <c r="B468" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C468" s="1">
         <v>45796</v>
@@ -22697,7 +22690,7 @@
         <v>71</v>
       </c>
       <c r="B469" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C469" s="1">
         <v>45347</v>
@@ -22738,7 +22731,7 @@
         <v>60</v>
       </c>
       <c r="B470" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C470" s="1">
         <v>46007</v>
@@ -22779,7 +22772,7 @@
         <v>52</v>
       </c>
       <c r="B471" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C471" s="1">
         <v>45919</v>
@@ -22820,7 +22813,7 @@
         <v>84</v>
       </c>
       <c r="B472" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C472" s="1">
         <v>45802</v>
@@ -22861,7 +22854,7 @@
         <v>43</v>
       </c>
       <c r="B473" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C473" s="1">
         <v>45394</v>
@@ -22902,7 +22895,7 @@
         <v>142</v>
       </c>
       <c r="B474" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C474" s="1">
         <v>45472</v>
@@ -22943,7 +22936,7 @@
         <v>13</v>
       </c>
       <c r="B475" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C475" s="1">
         <v>45699</v>
@@ -22984,7 +22977,7 @@
         <v>60</v>
       </c>
       <c r="B476" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C476" s="1">
         <v>45558</v>
@@ -23025,7 +23018,7 @@
         <v>79</v>
       </c>
       <c r="B477" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C477" s="1">
         <v>45987</v>
@@ -23066,7 +23059,7 @@
         <v>84</v>
       </c>
       <c r="B478" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C478" s="1">
         <v>45981</v>
@@ -23107,7 +23100,7 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C479" s="1">
         <v>45947</v>
@@ -23148,7 +23141,7 @@
         <v>55</v>
       </c>
       <c r="B480" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C480" s="1">
         <v>45525</v>
@@ -23189,7 +23182,7 @@
         <v>60</v>
       </c>
       <c r="B481" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C481" s="1">
         <v>45893</v>
@@ -23230,7 +23223,7 @@
         <v>13</v>
       </c>
       <c r="B482" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C482" s="1">
         <v>45507</v>
@@ -23271,7 +23264,7 @@
         <v>123</v>
       </c>
       <c r="B483" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C483" s="1">
         <v>45828</v>
@@ -23312,7 +23305,7 @@
         <v>26</v>
       </c>
       <c r="B484" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C484" s="1">
         <v>45545</v>
@@ -23353,7 +23346,7 @@
         <v>84</v>
       </c>
       <c r="B485" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C485" s="1">
         <v>45779</v>
@@ -23394,7 +23387,7 @@
         <v>60</v>
       </c>
       <c r="B486" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C486" s="1">
         <v>45828</v>
@@ -23435,7 +23428,7 @@
         <v>84</v>
       </c>
       <c r="B487" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C487" s="1">
         <v>45558</v>
@@ -23476,7 +23469,7 @@
         <v>26</v>
       </c>
       <c r="B488" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C488" s="1">
         <v>45839</v>
@@ -23517,7 +23510,7 @@
         <v>71</v>
       </c>
       <c r="B489" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C489" s="1">
         <v>45853</v>
@@ -23558,7 +23551,7 @@
         <v>104</v>
       </c>
       <c r="B490" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C490" s="1">
         <v>45561</v>
@@ -23599,7 +23592,7 @@
         <v>26</v>
       </c>
       <c r="B491" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C491" s="1">
         <v>45567</v>
@@ -23640,7 +23633,7 @@
         <v>60</v>
       </c>
       <c r="B492" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C492" s="1">
         <v>46009</v>
@@ -23681,7 +23674,7 @@
         <v>55</v>
       </c>
       <c r="B493" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C493" s="1">
         <v>45580</v>
@@ -23722,7 +23715,7 @@
         <v>142</v>
       </c>
       <c r="B494" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C494" s="1">
         <v>45642</v>
@@ -23763,7 +23756,7 @@
         <v>52</v>
       </c>
       <c r="B495" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C495" s="1">
         <v>45441</v>
@@ -23804,7 +23797,7 @@
         <v>104</v>
       </c>
       <c r="B496" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C496" s="1">
         <v>45416</v>
@@ -23845,7 +23838,7 @@
         <v>63</v>
       </c>
       <c r="B497" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C497" s="1">
         <v>45690</v>
@@ -23886,7 +23879,7 @@
         <v>142</v>
       </c>
       <c r="B498" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C498" s="1">
         <v>45495</v>
@@ -23927,7 +23920,7 @@
         <v>123</v>
       </c>
       <c r="B499" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C499" s="1">
         <v>45574</v>
@@ -23968,7 +23961,7 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C500" s="1">
         <v>45383</v>
@@ -24009,7 +24002,7 @@
         <v>32</v>
       </c>
       <c r="B501" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C501" s="1">
         <v>45952</v>
@@ -24050,7 +24043,7 @@
         <v>84</v>
       </c>
       <c r="B502" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C502" s="1">
         <v>45489</v>
@@ -24091,7 +24084,7 @@
         <v>26</v>
       </c>
       <c r="B503" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C503" s="1">
         <v>46005</v>
@@ -24132,7 +24125,7 @@
         <v>55</v>
       </c>
       <c r="B504" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C504" s="1">
         <v>45835</v>
@@ -24173,7 +24166,7 @@
         <v>104</v>
       </c>
       <c r="B505" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C505" s="1">
         <v>45311</v>
@@ -24214,7 +24207,7 @@
         <v>104</v>
       </c>
       <c r="B506" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C506" s="1">
         <v>45828</v>
@@ -24255,7 +24248,7 @@
         <v>79</v>
       </c>
       <c r="B507" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C507" s="1">
         <v>45966</v>
@@ -24296,7 +24289,7 @@
         <v>63</v>
       </c>
       <c r="B508" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C508" s="1">
         <v>45324</v>
@@ -24337,7 +24330,7 @@
         <v>84</v>
       </c>
       <c r="B509" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C509" s="1">
         <v>45912</v>
@@ -24378,7 +24371,7 @@
         <v>84</v>
       </c>
       <c r="B510" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C510" s="1">
         <v>45669</v>
@@ -24419,7 +24412,7 @@
         <v>63</v>
       </c>
       <c r="B511" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C511" s="1">
         <v>45391</v>
@@ -24460,7 +24453,7 @@
         <v>55</v>
       </c>
       <c r="B512" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C512" s="1">
         <v>45400</v>
@@ -24501,7 +24494,7 @@
         <v>55</v>
       </c>
       <c r="B513" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C513" s="1">
         <v>45808</v>
@@ -24542,7 +24535,7 @@
         <v>52</v>
       </c>
       <c r="B514" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C514" s="1">
         <v>45714</v>
@@ -24583,7 +24576,7 @@
         <v>13</v>
       </c>
       <c r="B515" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C515" s="1">
         <v>45755</v>
@@ -24624,7 +24617,7 @@
         <v>26</v>
       </c>
       <c r="B516" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C516" s="1">
         <v>45599</v>
@@ -24665,7 +24658,7 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C517" s="1">
         <v>45330</v>
@@ -24706,7 +24699,7 @@
         <v>13</v>
       </c>
       <c r="B518" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C518" s="1">
         <v>45386</v>
@@ -24788,7 +24781,7 @@
         <v>32</v>
       </c>
       <c r="B520" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C520" s="1">
         <v>45648</v>
@@ -24829,7 +24822,7 @@
         <v>123</v>
       </c>
       <c r="B521" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C521" s="1">
         <v>45347</v>
@@ -24870,7 +24863,7 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C522" s="1">
         <v>45981</v>
@@ -24911,7 +24904,7 @@
         <v>104</v>
       </c>
       <c r="B523" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C523" s="1">
         <v>45427</v>
@@ -24952,7 +24945,7 @@
         <v>104</v>
       </c>
       <c r="B524" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C524" s="1">
         <v>45736</v>
@@ -24993,7 +24986,7 @@
         <v>71</v>
       </c>
       <c r="B525" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C525" s="1">
         <v>45365</v>
@@ -25034,7 +25027,7 @@
         <v>84</v>
       </c>
       <c r="B526" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C526" s="1">
         <v>45620</v>
@@ -25075,7 +25068,7 @@
         <v>60</v>
       </c>
       <c r="B527" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C527" s="1">
         <v>45743</v>
@@ -25116,7 +25109,7 @@
         <v>32</v>
       </c>
       <c r="B528" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C528" s="1">
         <v>45927</v>
@@ -25157,7 +25150,7 @@
         <v>123</v>
       </c>
       <c r="B529" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C529" s="1">
         <v>45506</v>
@@ -25198,7 +25191,7 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C530" s="1">
         <v>45677</v>
@@ -25239,7 +25232,7 @@
         <v>13</v>
       </c>
       <c r="B531" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C531" s="1">
         <v>45768</v>
@@ -25280,7 +25273,7 @@
         <v>123</v>
       </c>
       <c r="B532" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C532" s="1">
         <v>45956</v>
@@ -25321,7 +25314,7 @@
         <v>37</v>
       </c>
       <c r="B533" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C533" s="1">
         <v>45495</v>
@@ -25362,7 +25355,7 @@
         <v>142</v>
       </c>
       <c r="B534" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C534" s="1">
         <v>45452</v>
@@ -25403,7 +25396,7 @@
         <v>13</v>
       </c>
       <c r="B535" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C535" s="1">
         <v>45932</v>
@@ -25444,7 +25437,7 @@
         <v>52</v>
       </c>
       <c r="B536" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C536" s="1">
         <v>45964</v>
@@ -25485,7 +25478,7 @@
         <v>129</v>
       </c>
       <c r="B537" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C537" s="1">
         <v>45878</v>
@@ -25526,7 +25519,7 @@
         <v>63</v>
       </c>
       <c r="B538" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C538" s="1">
         <v>45608</v>
@@ -25567,7 +25560,7 @@
         <v>37</v>
       </c>
       <c r="B539" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C539" s="1">
         <v>45413</v>
@@ -25608,7 +25601,7 @@
         <v>129</v>
       </c>
       <c r="B540" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C540" s="1">
         <v>45745</v>
@@ -25649,7 +25642,7 @@
         <v>13</v>
       </c>
       <c r="B541" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C541" s="1">
         <v>45902</v>
@@ -25690,7 +25683,7 @@
         <v>142</v>
       </c>
       <c r="B542" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C542" s="1">
         <v>45480</v>
@@ -25731,7 +25724,7 @@
         <v>13</v>
       </c>
       <c r="B543" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C543" s="1">
         <v>45519</v>
@@ -25772,7 +25765,7 @@
         <v>52</v>
       </c>
       <c r="B544" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C544" s="1">
         <v>45544</v>
@@ -25813,7 +25806,7 @@
         <v>104</v>
       </c>
       <c r="B545" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C545" s="1">
         <v>45829</v>
@@ -25854,7 +25847,7 @@
         <v>104</v>
       </c>
       <c r="B546" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C546" s="1">
         <v>45863</v>
@@ -25895,7 +25888,7 @@
         <v>26</v>
       </c>
       <c r="B547" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C547" s="1">
         <v>45462</v>
@@ -25936,7 +25929,7 @@
         <v>37</v>
       </c>
       <c r="B548" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C548" s="1">
         <v>45407</v>
@@ -25977,7 +25970,7 @@
         <v>55</v>
       </c>
       <c r="B549" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C549" s="1">
         <v>45896</v>
@@ -26059,7 +26052,7 @@
         <v>55</v>
       </c>
       <c r="B551" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C551" s="1">
         <v>45855</v>
@@ -26100,7 +26093,7 @@
         <v>55</v>
       </c>
       <c r="B552" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C552" s="1">
         <v>45475</v>
@@ -26141,7 +26134,7 @@
         <v>79</v>
       </c>
       <c r="B553" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C553" s="1">
         <v>45499</v>
@@ -26182,7 +26175,7 @@
         <v>123</v>
       </c>
       <c r="B554" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C554" s="1">
         <v>45535</v>
@@ -26223,7 +26216,7 @@
         <v>123</v>
       </c>
       <c r="B555" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C555" s="1">
         <v>45852</v>
@@ -26264,7 +26257,7 @@
         <v>32</v>
       </c>
       <c r="B556" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C556" s="1">
         <v>45329</v>
@@ -26305,7 +26298,7 @@
         <v>32</v>
       </c>
       <c r="B557" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C557" s="1">
         <v>45718</v>
@@ -26387,7 +26380,7 @@
         <v>129</v>
       </c>
       <c r="B559" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C559" s="1">
         <v>45591</v>
@@ -26428,7 +26421,7 @@
         <v>32</v>
       </c>
       <c r="B560" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C560" s="1">
         <v>45877</v>
@@ -26469,7 +26462,7 @@
         <v>52</v>
       </c>
       <c r="B561" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C561" s="1">
         <v>45830</v>
@@ -26510,7 +26503,7 @@
         <v>142</v>
       </c>
       <c r="B562" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C562" s="1">
         <v>45916</v>
@@ -26551,7 +26544,7 @@
         <v>63</v>
       </c>
       <c r="B563" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C563" s="1">
         <v>45715</v>
@@ -26592,7 +26585,7 @@
         <v>26</v>
       </c>
       <c r="B564" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C564" s="1">
         <v>45361</v>
@@ -26633,7 +26626,7 @@
         <v>52</v>
       </c>
       <c r="B565" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C565" s="1">
         <v>45874</v>
@@ -26674,7 +26667,7 @@
         <v>142</v>
       </c>
       <c r="B566" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C566" s="1">
         <v>45953</v>
@@ -26715,7 +26708,7 @@
         <v>129</v>
       </c>
       <c r="B567" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C567" s="1">
         <v>45825</v>
@@ -26756,7 +26749,7 @@
         <v>84</v>
       </c>
       <c r="B568" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C568" s="1">
         <v>45444</v>
@@ -26797,7 +26790,7 @@
         <v>104</v>
       </c>
       <c r="B569" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C569" s="1">
         <v>45901</v>
@@ -26838,7 +26831,7 @@
         <v>71</v>
       </c>
       <c r="B570" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C570" s="1">
         <v>45754</v>
@@ -26879,7 +26872,7 @@
         <v>37</v>
       </c>
       <c r="B571" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C571" s="1">
         <v>45810</v>
@@ -26920,7 +26913,7 @@
         <v>26</v>
       </c>
       <c r="B572" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C572" s="1">
         <v>45438</v>
@@ -26961,7 +26954,7 @@
         <v>79</v>
       </c>
       <c r="B573" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C573" s="1">
         <v>45610</v>
@@ -27002,7 +26995,7 @@
         <v>26</v>
       </c>
       <c r="B574" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C574" s="1">
         <v>45883</v>
@@ -27043,7 +27036,7 @@
         <v>79</v>
       </c>
       <c r="B575" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C575" s="1">
         <v>45444</v>
@@ -27084,7 +27077,7 @@
         <v>84</v>
       </c>
       <c r="B576" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C576" s="1">
         <v>45569</v>
@@ -27125,7 +27118,7 @@
         <v>60</v>
       </c>
       <c r="B577" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C577" s="1">
         <v>45425</v>
@@ -27166,7 +27159,7 @@
         <v>55</v>
       </c>
       <c r="B578" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C578" s="1">
         <v>45923</v>
@@ -27207,7 +27200,7 @@
         <v>60</v>
       </c>
       <c r="B579" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C579" s="1">
         <v>45387</v>
@@ -27248,7 +27241,7 @@
         <v>71</v>
       </c>
       <c r="B580" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C580" s="1">
         <v>45439</v>
@@ -27289,7 +27282,7 @@
         <v>60</v>
       </c>
       <c r="B581" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C581" s="1">
         <v>45322</v>
@@ -27330,7 +27323,7 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C582" s="1">
         <v>45397</v>
@@ -27371,7 +27364,7 @@
         <v>104</v>
       </c>
       <c r="B583" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C583" s="1">
         <v>45536</v>
@@ -27412,7 +27405,7 @@
         <v>129</v>
       </c>
       <c r="B584" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C584" s="1">
         <v>45872</v>
@@ -27453,7 +27446,7 @@
         <v>142</v>
       </c>
       <c r="B585" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C585" s="1">
         <v>45898</v>
@@ -27494,7 +27487,7 @@
         <v>37</v>
       </c>
       <c r="B586" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C586" s="1">
         <v>45993</v>
@@ -27535,7 +27528,7 @@
         <v>123</v>
       </c>
       <c r="B587" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C587" s="1">
         <v>45968</v>
@@ -27576,7 +27569,7 @@
         <v>52</v>
       </c>
       <c r="B588" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C588" s="1">
         <v>45875</v>
@@ -27617,7 +27610,7 @@
         <v>104</v>
       </c>
       <c r="B589" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C589" s="1">
         <v>45593</v>
@@ -27658,7 +27651,7 @@
         <v>79</v>
       </c>
       <c r="B590" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C590" s="1">
         <v>45323</v>
@@ -27699,7 +27692,7 @@
         <v>104</v>
       </c>
       <c r="B591" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C591" s="1">
         <v>45850</v>
@@ -27740,7 +27733,7 @@
         <v>129</v>
       </c>
       <c r="B592" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C592" s="1">
         <v>45587</v>
@@ -27781,7 +27774,7 @@
         <v>129</v>
       </c>
       <c r="B593" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C593" s="1">
         <v>45378</v>
@@ -27822,7 +27815,7 @@
         <v>55</v>
       </c>
       <c r="B594" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C594" s="1">
         <v>45813</v>
@@ -27863,7 +27856,7 @@
         <v>123</v>
       </c>
       <c r="B595" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C595" s="1">
         <v>45534</v>
@@ -27904,7 +27897,7 @@
         <v>142</v>
       </c>
       <c r="B596" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C596" s="1">
         <v>45407</v>
@@ -27945,7 +27938,7 @@
         <v>60</v>
       </c>
       <c r="B597" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C597" s="1">
         <v>45372</v>
@@ -27986,7 +27979,7 @@
         <v>26</v>
       </c>
       <c r="B598" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C598" s="1">
         <v>45643</v>
@@ -28027,7 +28020,7 @@
         <v>129</v>
       </c>
       <c r="B599" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C599" s="1">
         <v>45593</v>
@@ -28068,7 +28061,7 @@
         <v>32</v>
       </c>
       <c r="B600" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C600" s="1">
         <v>45884</v>
@@ -28101,7 +28094,7 @@
         <v>8.7400000000000005E-2</v>
       </c>
       <c r="M600" t="s">
-        <v>291</v>
+        <v>54</v>
       </c>
     </row>
     <row r="601" spans="1:13" x14ac:dyDescent="0.3">
@@ -28109,7 +28102,7 @@
         <v>37</v>
       </c>
       <c r="B601" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C601" s="1">
         <v>45809</v>
@@ -28150,7 +28143,7 @@
         <v>79</v>
       </c>
       <c r="B602" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C602" s="1">
         <v>45897</v>
@@ -28191,7 +28184,7 @@
         <v>32</v>
       </c>
       <c r="B603" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C603" s="1">
         <v>45378</v>
@@ -28232,7 +28225,7 @@
         <v>71</v>
       </c>
       <c r="B604" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C604" s="1">
         <v>45944</v>
@@ -28273,7 +28266,7 @@
         <v>32</v>
       </c>
       <c r="B605" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C605" s="1">
         <v>45767</v>
@@ -28314,7 +28307,7 @@
         <v>104</v>
       </c>
       <c r="B606" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C606" s="1">
         <v>45777</v>
@@ -28355,7 +28348,7 @@
         <v>52</v>
       </c>
       <c r="B607" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C607" s="1">
         <v>45991</v>
@@ -28396,7 +28389,7 @@
         <v>52</v>
       </c>
       <c r="B608" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C608" s="1">
         <v>45565</v>
@@ -28437,7 +28430,7 @@
         <v>63</v>
       </c>
       <c r="B609" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C609" s="1">
         <v>45637</v>
@@ -28478,7 +28471,7 @@
         <v>79</v>
       </c>
       <c r="B610" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C610" s="1">
         <v>45398</v>
@@ -28519,7 +28512,7 @@
         <v>32</v>
       </c>
       <c r="B611" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C611" s="1">
         <v>45905</v>
@@ -28560,7 +28553,7 @@
         <v>55</v>
       </c>
       <c r="B612" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C612" s="1">
         <v>46004</v>
@@ -28601,7 +28594,7 @@
         <v>129</v>
       </c>
       <c r="B613" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C613" s="1">
         <v>45555</v>
@@ -28642,7 +28635,7 @@
         <v>13</v>
       </c>
       <c r="B614" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C614" s="1">
         <v>45743</v>
@@ -28683,7 +28676,7 @@
         <v>129</v>
       </c>
       <c r="B615" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C615" s="1">
         <v>45920</v>
@@ -28724,7 +28717,7 @@
         <v>60</v>
       </c>
       <c r="B616" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C616" s="1">
         <v>45801</v>
@@ -28765,7 +28758,7 @@
         <v>123</v>
       </c>
       <c r="B617" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C617" s="1">
         <v>46016</v>
@@ -28806,7 +28799,7 @@
         <v>71</v>
       </c>
       <c r="B618" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C618" s="1">
         <v>45685</v>
@@ -28847,7 +28840,7 @@
         <v>104</v>
       </c>
       <c r="B619" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C619" s="1">
         <v>45939</v>
@@ -28888,7 +28881,7 @@
         <v>63</v>
       </c>
       <c r="B620" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C620" s="1">
         <v>45859</v>
@@ -28929,7 +28922,7 @@
         <v>142</v>
       </c>
       <c r="B621" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C621" s="1">
         <v>45939</v>
@@ -28970,7 +28963,7 @@
         <v>142</v>
       </c>
       <c r="B622" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C622" s="1">
         <v>45356</v>
@@ -29011,7 +29004,7 @@
         <v>32</v>
       </c>
       <c r="B623" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C623" s="1">
         <v>45349</v>
@@ -29052,7 +29045,7 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C624" s="1">
         <v>45365</v>
@@ -29093,7 +29086,7 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C625" s="1">
         <v>45468</v>
@@ -29134,7 +29127,7 @@
         <v>79</v>
       </c>
       <c r="B626" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C626" s="1">
         <v>45801</v>
@@ -29175,7 +29168,7 @@
         <v>52</v>
       </c>
       <c r="B627" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C627" s="1">
         <v>45992</v>
@@ -29216,7 +29209,7 @@
         <v>55</v>
       </c>
       <c r="B628" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C628" s="1">
         <v>45356</v>
@@ -29257,7 +29250,7 @@
         <v>71</v>
       </c>
       <c r="B629" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C629" s="1">
         <v>45428</v>
@@ -29298,7 +29291,7 @@
         <v>55</v>
       </c>
       <c r="B630" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C630" s="1">
         <v>46015</v>
@@ -29339,7 +29332,7 @@
         <v>60</v>
       </c>
       <c r="B631" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C631" s="1">
         <v>45536</v>
@@ -29380,7 +29373,7 @@
         <v>26</v>
       </c>
       <c r="B632" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C632" s="1">
         <v>45720</v>
@@ -29421,7 +29414,7 @@
         <v>84</v>
       </c>
       <c r="B633" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C633" s="1">
         <v>45811</v>
@@ -29462,7 +29455,7 @@
         <v>142</v>
       </c>
       <c r="B634" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C634" s="1">
         <v>45472</v>
@@ -29503,7 +29496,7 @@
         <v>60</v>
       </c>
       <c r="B635" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C635" s="1">
         <v>45398</v>
@@ -29544,7 +29537,7 @@
         <v>71</v>
       </c>
       <c r="B636" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C636" s="1">
         <v>45898</v>
@@ -29585,7 +29578,7 @@
         <v>52</v>
       </c>
       <c r="B637" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C637" s="1">
         <v>45392</v>
@@ -29626,7 +29619,7 @@
         <v>142</v>
       </c>
       <c r="B638" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C638" s="1">
         <v>45738</v>
@@ -29667,7 +29660,7 @@
         <v>84</v>
       </c>
       <c r="B639" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C639" s="1">
         <v>45499</v>
@@ -29708,7 +29701,7 @@
         <v>60</v>
       </c>
       <c r="B640" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C640" s="1">
         <v>45467</v>
@@ -29749,7 +29742,7 @@
         <v>55</v>
       </c>
       <c r="B641" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C641" s="1">
         <v>45380</v>
@@ -29790,7 +29783,7 @@
         <v>129</v>
       </c>
       <c r="B642" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C642" s="1">
         <v>45545</v>
@@ -29831,7 +29824,7 @@
         <v>123</v>
       </c>
       <c r="B643" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C643" s="1">
         <v>45337</v>
@@ -29872,7 +29865,7 @@
         <v>60</v>
       </c>
       <c r="B644" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C644" s="1">
         <v>45538</v>
@@ -29913,7 +29906,7 @@
         <v>84</v>
       </c>
       <c r="B645" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C645" s="1">
         <v>45536</v>
@@ -29954,7 +29947,7 @@
         <v>123</v>
       </c>
       <c r="B646" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C646" s="1">
         <v>45766</v>
@@ -29995,7 +29988,7 @@
         <v>104</v>
       </c>
       <c r="B647" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C647" s="1">
         <v>45835</v>
@@ -30036,7 +30029,7 @@
         <v>37</v>
       </c>
       <c r="B648" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C648" s="1">
         <v>45348</v>
@@ -30077,7 +30070,7 @@
         <v>84</v>
       </c>
       <c r="B649" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C649" s="1">
         <v>45955</v>
@@ -30118,7 +30111,7 @@
         <v>142</v>
       </c>
       <c r="B650" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C650" s="1">
         <v>45522</v>
@@ -30159,7 +30152,7 @@
         <v>84</v>
       </c>
       <c r="B651" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C651" s="1">
         <v>45789</v>
@@ -30200,7 +30193,7 @@
         <v>26</v>
       </c>
       <c r="B652" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C652" s="1">
         <v>45927</v>
@@ -30241,7 +30234,7 @@
         <v>37</v>
       </c>
       <c r="B653" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C653" s="1">
         <v>45460</v>
@@ -30323,7 +30316,7 @@
         <v>63</v>
       </c>
       <c r="B655" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C655" s="1">
         <v>45314</v>
@@ -30364,7 +30357,7 @@
         <v>142</v>
       </c>
       <c r="B656" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C656" s="1">
         <v>45853</v>
@@ -30405,7 +30398,7 @@
         <v>71</v>
       </c>
       <c r="B657" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C657" s="1">
         <v>45672</v>
@@ -30446,7 +30439,7 @@
         <v>26</v>
       </c>
       <c r="B658" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C658" s="1">
         <v>45471</v>
@@ -30487,7 +30480,7 @@
         <v>13</v>
       </c>
       <c r="B659" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C659" s="1">
         <v>45480</v>
@@ -30528,7 +30521,7 @@
         <v>55</v>
       </c>
       <c r="B660" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C660" s="1">
         <v>45600</v>
@@ -30569,7 +30562,7 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C661" s="1">
         <v>45851</v>
@@ -30610,7 +30603,7 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C662" s="1">
         <v>45638</v>
@@ -30651,7 +30644,7 @@
         <v>71</v>
       </c>
       <c r="B663" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C663" s="1">
         <v>45657</v>
@@ -30692,7 +30685,7 @@
         <v>63</v>
       </c>
       <c r="B664" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C664" s="1">
         <v>45377</v>
@@ -30733,7 +30726,7 @@
         <v>32</v>
       </c>
       <c r="B665" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C665" s="1">
         <v>45699</v>
@@ -30774,7 +30767,7 @@
         <v>60</v>
       </c>
       <c r="B666" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C666" s="1">
         <v>45512</v>
@@ -30815,7 +30808,7 @@
         <v>129</v>
       </c>
       <c r="B667" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C667" s="1">
         <v>45893</v>
@@ -30856,7 +30849,7 @@
         <v>37</v>
       </c>
       <c r="B668" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C668" s="1">
         <v>45382</v>
@@ -30897,7 +30890,7 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C669" s="1">
         <v>45482</v>
@@ -30979,7 +30972,7 @@
         <v>79</v>
       </c>
       <c r="B671" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C671" s="1">
         <v>45719</v>
@@ -31020,7 +31013,7 @@
         <v>84</v>
       </c>
       <c r="B672" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C672" s="1">
         <v>45871</v>
@@ -31061,7 +31054,7 @@
         <v>123</v>
       </c>
       <c r="B673" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C673" s="1">
         <v>45458</v>
@@ -31102,7 +31095,7 @@
         <v>32</v>
       </c>
       <c r="B674" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C674" s="1">
         <v>45661</v>
@@ -31143,7 +31136,7 @@
         <v>63</v>
       </c>
       <c r="B675" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C675" s="1">
         <v>45388</v>
@@ -31184,7 +31177,7 @@
         <v>13</v>
       </c>
       <c r="B676" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C676" s="1">
         <v>45390</v>
@@ -31225,7 +31218,7 @@
         <v>129</v>
       </c>
       <c r="B677" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C677" s="1">
         <v>45458</v>
@@ -31266,7 +31259,7 @@
         <v>79</v>
       </c>
       <c r="B678" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C678" s="1">
         <v>45763</v>
@@ -31307,7 +31300,7 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C679" s="1">
         <v>45903</v>
@@ -31348,7 +31341,7 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C680" s="1">
         <v>45606</v>
@@ -31389,7 +31382,7 @@
         <v>123</v>
       </c>
       <c r="B681" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C681" s="1">
         <v>45733</v>
@@ -31430,7 +31423,7 @@
         <v>79</v>
       </c>
       <c r="B682" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C682" s="1">
         <v>45336</v>
@@ -31471,7 +31464,7 @@
         <v>63</v>
       </c>
       <c r="B683" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C683" s="1">
         <v>45481</v>
@@ -31512,7 +31505,7 @@
         <v>84</v>
       </c>
       <c r="B684" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C684" s="1">
         <v>45456</v>
@@ -31553,7 +31546,7 @@
         <v>63</v>
       </c>
       <c r="B685" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C685" s="1">
         <v>45580</v>
@@ -31594,7 +31587,7 @@
         <v>84</v>
       </c>
       <c r="B686" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C686" s="1">
         <v>45742</v>
@@ -31635,7 +31628,7 @@
         <v>129</v>
       </c>
       <c r="B687" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C687" s="1">
         <v>45613</v>
@@ -31676,7 +31669,7 @@
         <v>32</v>
       </c>
       <c r="B688" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C688" s="1">
         <v>45627</v>
@@ -31717,7 +31710,7 @@
         <v>71</v>
       </c>
       <c r="B689" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C689" s="1">
         <v>45589</v>
@@ -31758,7 +31751,7 @@
         <v>55</v>
       </c>
       <c r="B690" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C690" s="1">
         <v>45982</v>
@@ -31799,7 +31792,7 @@
         <v>104</v>
       </c>
       <c r="B691" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C691" s="1">
         <v>46003</v>
@@ -31840,7 +31833,7 @@
         <v>104</v>
       </c>
       <c r="B692" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C692" s="1">
         <v>45530</v>
@@ -31881,7 +31874,7 @@
         <v>84</v>
       </c>
       <c r="B693" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C693" s="1">
         <v>45974</v>
@@ -31922,7 +31915,7 @@
         <v>13</v>
       </c>
       <c r="B694" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C694" s="1">
         <v>45801</v>
@@ -31963,7 +31956,7 @@
         <v>55</v>
       </c>
       <c r="B695" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C695" s="1">
         <v>45911</v>
@@ -32004,7 +31997,7 @@
         <v>142</v>
       </c>
       <c r="B696" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C696" s="1">
         <v>45498</v>
@@ -32045,7 +32038,7 @@
         <v>123</v>
       </c>
       <c r="B697" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C697" s="1">
         <v>45732</v>
@@ -32086,7 +32079,7 @@
         <v>55</v>
       </c>
       <c r="B698" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C698" s="1">
         <v>46015</v>
@@ -32127,7 +32120,7 @@
         <v>142</v>
       </c>
       <c r="B699" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C699" s="1">
         <v>45877</v>
@@ -32168,7 +32161,7 @@
         <v>104</v>
       </c>
       <c r="B700" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C700" s="1">
         <v>45583</v>
@@ -32209,7 +32202,7 @@
         <v>123</v>
       </c>
       <c r="B701" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C701" s="1">
         <v>45681</v>
@@ -32250,7 +32243,7 @@
         <v>71</v>
       </c>
       <c r="B702" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C702" s="1">
         <v>45898</v>
@@ -32291,7 +32284,7 @@
         <v>32</v>
       </c>
       <c r="B703" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C703" s="1">
         <v>45965</v>
@@ -32332,7 +32325,7 @@
         <v>52</v>
       </c>
       <c r="B704" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C704" s="1">
         <v>45876</v>
@@ -32373,7 +32366,7 @@
         <v>52</v>
       </c>
       <c r="B705" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C705" s="1">
         <v>45806</v>
@@ -32414,7 +32407,7 @@
         <v>63</v>
       </c>
       <c r="B706" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C706" s="1">
         <v>45563</v>
@@ -32455,7 +32448,7 @@
         <v>79</v>
       </c>
       <c r="B707" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C707" s="1">
         <v>45571</v>
@@ -32496,7 +32489,7 @@
         <v>26</v>
       </c>
       <c r="B708" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C708" s="1">
         <v>45599</v>
@@ -32537,7 +32530,7 @@
         <v>55</v>
       </c>
       <c r="B709" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C709" s="1">
         <v>45934</v>
@@ -32578,7 +32571,7 @@
         <v>13</v>
       </c>
       <c r="B710" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C710" s="1">
         <v>45921</v>
@@ -32619,7 +32612,7 @@
         <v>43</v>
       </c>
       <c r="B711" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C711" s="1">
         <v>45737</v>
@@ -32660,7 +32653,7 @@
         <v>55</v>
       </c>
       <c r="B712" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C712" s="1">
         <v>45995</v>
@@ -32701,7 +32694,7 @@
         <v>60</v>
       </c>
       <c r="B713" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C713" s="1">
         <v>45865</v>
@@ -32742,7 +32735,7 @@
         <v>13</v>
       </c>
       <c r="B714" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C714" s="1">
         <v>45951</v>
@@ -32783,7 +32776,7 @@
         <v>26</v>
       </c>
       <c r="B715" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C715" s="1">
         <v>45708</v>
@@ -32824,7 +32817,7 @@
         <v>13</v>
       </c>
       <c r="B716" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C716" s="1">
         <v>45384</v>
@@ -32865,7 +32858,7 @@
         <v>129</v>
       </c>
       <c r="B717" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C717" s="1">
         <v>45439</v>
@@ -32906,7 +32899,7 @@
         <v>142</v>
       </c>
       <c r="B718" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C718" s="1">
         <v>45675</v>
@@ -32947,7 +32940,7 @@
         <v>84</v>
       </c>
       <c r="B719" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C719" s="1">
         <v>45668</v>
@@ -32988,7 +32981,7 @@
         <v>71</v>
       </c>
       <c r="B720" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C720" s="1">
         <v>45857</v>
@@ -33029,7 +33022,7 @@
         <v>60</v>
       </c>
       <c r="B721" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C721" s="1">
         <v>45300</v>
@@ -33070,7 +33063,7 @@
         <v>55</v>
       </c>
       <c r="B722" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C722" s="1">
         <v>45938</v>
@@ -33111,7 +33104,7 @@
         <v>142</v>
       </c>
       <c r="B723" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C723" s="1">
         <v>45632</v>
@@ -33152,7 +33145,7 @@
         <v>52</v>
       </c>
       <c r="B724" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C724" s="1">
         <v>46003</v>
@@ -33193,7 +33186,7 @@
         <v>104</v>
       </c>
       <c r="B725" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C725" s="1">
         <v>45935</v>
@@ -33234,7 +33227,7 @@
         <v>129</v>
       </c>
       <c r="B726" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C726" s="1">
         <v>45754</v>
@@ -33275,7 +33268,7 @@
         <v>63</v>
       </c>
       <c r="B727" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C727" s="1">
         <v>45716</v>
@@ -33316,7 +33309,7 @@
         <v>123</v>
       </c>
       <c r="B728" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C728" s="1">
         <v>45383</v>
@@ -33357,7 +33350,7 @@
         <v>43</v>
       </c>
       <c r="B729" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C729" s="1">
         <v>45668</v>
@@ -33398,7 +33391,7 @@
         <v>142</v>
       </c>
       <c r="B730" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C730" s="1">
         <v>45521</v>
@@ -33439,7 +33432,7 @@
         <v>63</v>
       </c>
       <c r="B731" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C731" s="1">
         <v>45581</v>
@@ -33480,7 +33473,7 @@
         <v>71</v>
       </c>
       <c r="B732" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C732" s="1">
         <v>45546</v>
@@ -33521,7 +33514,7 @@
         <v>104</v>
       </c>
       <c r="B733" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C733" s="1">
         <v>46022</v>
@@ -33562,7 +33555,7 @@
         <v>52</v>
       </c>
       <c r="B734" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C734" s="1">
         <v>45774</v>
@@ -33603,7 +33596,7 @@
         <v>104</v>
       </c>
       <c r="B735" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C735" s="1">
         <v>45696</v>
@@ -33644,7 +33637,7 @@
         <v>52</v>
       </c>
       <c r="B736" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C736" s="1">
         <v>45427</v>
@@ -33685,7 +33678,7 @@
         <v>43</v>
       </c>
       <c r="B737" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C737" s="1">
         <v>45579</v>
@@ -33726,7 +33719,7 @@
         <v>52</v>
       </c>
       <c r="B738" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C738" s="1">
         <v>45460</v>
@@ -33767,7 +33760,7 @@
         <v>32</v>
       </c>
       <c r="B739" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C739" s="1">
         <v>45444</v>
@@ -33808,7 +33801,7 @@
         <v>79</v>
       </c>
       <c r="B740" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C740" s="1">
         <v>45333</v>
@@ -33849,7 +33842,7 @@
         <v>79</v>
       </c>
       <c r="B741" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C741" s="1">
         <v>45387</v>
@@ -33890,7 +33883,7 @@
         <v>63</v>
       </c>
       <c r="B742" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C742" s="1">
         <v>45830</v>
@@ -33931,7 +33924,7 @@
         <v>123</v>
       </c>
       <c r="B743" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C743" s="1">
         <v>45989</v>
@@ -33972,7 +33965,7 @@
         <v>123</v>
       </c>
       <c r="B744" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C744" s="1">
         <v>45763</v>
@@ -34013,7 +34006,7 @@
         <v>60</v>
       </c>
       <c r="B745" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C745" s="1">
         <v>45874</v>
@@ -34054,7 +34047,7 @@
         <v>37</v>
       </c>
       <c r="B746" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C746" s="1">
         <v>45908</v>
@@ -34095,7 +34088,7 @@
         <v>37</v>
       </c>
       <c r="B747" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C747" s="1">
         <v>45505</v>
@@ -34136,7 +34129,7 @@
         <v>79</v>
       </c>
       <c r="B748" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C748" s="1">
         <v>45794</v>
@@ -34177,7 +34170,7 @@
         <v>63</v>
       </c>
       <c r="B749" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C749" s="1">
         <v>45748</v>
@@ -34218,7 +34211,7 @@
         <v>55</v>
       </c>
       <c r="B750" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C750" s="1">
         <v>45937</v>
@@ -34259,7 +34252,7 @@
         <v>142</v>
       </c>
       <c r="B751" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C751" s="1">
         <v>45936</v>
@@ -34300,7 +34293,7 @@
         <v>43</v>
       </c>
       <c r="B752" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C752" s="1">
         <v>45992</v>
@@ -34341,7 +34334,7 @@
         <v>79</v>
       </c>
       <c r="B753" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C753" s="1">
         <v>45727</v>
@@ -34382,7 +34375,7 @@
         <v>123</v>
       </c>
       <c r="B754" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C754" s="1">
         <v>45969</v>
@@ -34423,7 +34416,7 @@
         <v>52</v>
       </c>
       <c r="B755" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C755" s="1">
         <v>45978</v>
@@ -34464,7 +34457,7 @@
         <v>63</v>
       </c>
       <c r="B756" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C756" s="1">
         <v>45372</v>
@@ -34505,7 +34498,7 @@
         <v>123</v>
       </c>
       <c r="B757" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C757" s="1">
         <v>45963</v>
@@ -34546,7 +34539,7 @@
         <v>26</v>
       </c>
       <c r="B758" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C758" s="1">
         <v>45999</v>
@@ -34587,7 +34580,7 @@
         <v>63</v>
       </c>
       <c r="B759" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C759" s="1">
         <v>45506</v>
@@ -34628,7 +34621,7 @@
         <v>63</v>
       </c>
       <c r="B760" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C760" s="1">
         <v>45600</v>
@@ -34669,7 +34662,7 @@
         <v>142</v>
       </c>
       <c r="B761" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C761" s="1">
         <v>45312</v>
@@ -34710,7 +34703,7 @@
         <v>52</v>
       </c>
       <c r="B762" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C762" s="1">
         <v>45397</v>
@@ -34751,7 +34744,7 @@
         <v>32</v>
       </c>
       <c r="B763" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C763" s="1">
         <v>45701</v>
@@ -34792,7 +34785,7 @@
         <v>71</v>
       </c>
       <c r="B764" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C764" s="1">
         <v>45832</v>
@@ -34833,7 +34826,7 @@
         <v>142</v>
       </c>
       <c r="B765" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C765" s="1">
         <v>45798</v>
@@ -34874,7 +34867,7 @@
         <v>84</v>
       </c>
       <c r="B766" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C766" s="1">
         <v>45529</v>
@@ -34915,7 +34908,7 @@
         <v>43</v>
       </c>
       <c r="B767" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C767" s="1">
         <v>46020</v>
@@ -34956,7 +34949,7 @@
         <v>63</v>
       </c>
       <c r="B768" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C768" s="1">
         <v>45999</v>
@@ -34997,7 +34990,7 @@
         <v>142</v>
       </c>
       <c r="B769" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C769" s="1">
         <v>45532</v>
@@ -35038,7 +35031,7 @@
         <v>55</v>
       </c>
       <c r="B770" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C770" s="1">
         <v>45324</v>
@@ -35079,7 +35072,7 @@
         <v>13</v>
       </c>
       <c r="B771" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C771" s="1">
         <v>45655</v>
@@ -35120,7 +35113,7 @@
         <v>32</v>
       </c>
       <c r="B772" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C772" s="1">
         <v>45760</v>
@@ -35202,7 +35195,7 @@
         <v>142</v>
       </c>
       <c r="B774" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C774" s="1">
         <v>45449</v>
@@ -35243,7 +35236,7 @@
         <v>123</v>
       </c>
       <c r="B775" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C775" s="1">
         <v>45777</v>
@@ -35284,7 +35277,7 @@
         <v>84</v>
       </c>
       <c r="B776" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C776" s="1">
         <v>45447</v>
@@ -35325,7 +35318,7 @@
         <v>60</v>
       </c>
       <c r="B777" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C777" s="1">
         <v>45990</v>
@@ -35366,7 +35359,7 @@
         <v>37</v>
       </c>
       <c r="B778" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C778" s="1">
         <v>45614</v>
@@ -35407,7 +35400,7 @@
         <v>32</v>
       </c>
       <c r="B779" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C779" s="1">
         <v>45594</v>
@@ -35448,7 +35441,7 @@
         <v>123</v>
       </c>
       <c r="B780" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C780" s="1">
         <v>45832</v>
@@ -35489,7 +35482,7 @@
         <v>60</v>
       </c>
       <c r="B781" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C781" s="1">
         <v>45956</v>
@@ -35530,7 +35523,7 @@
         <v>26</v>
       </c>
       <c r="B782" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C782" s="1">
         <v>45387</v>
@@ -35571,7 +35564,7 @@
         <v>13</v>
       </c>
       <c r="B783" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C783" s="1">
         <v>45603</v>
@@ -35612,7 +35605,7 @@
         <v>79</v>
       </c>
       <c r="B784" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C784" s="1">
         <v>45958</v>
@@ -35653,7 +35646,7 @@
         <v>71</v>
       </c>
       <c r="B785" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="C785" s="1">
         <v>45598</v>
@@ -35694,7 +35687,7 @@
         <v>52</v>
       </c>
       <c r="B786" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C786" s="1">
         <v>45888</v>
@@ -35735,7 +35728,7 @@
         <v>37</v>
       </c>
       <c r="B787" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C787" s="1">
         <v>45727</v>
@@ -35776,7 +35769,7 @@
         <v>104</v>
       </c>
       <c r="B788" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C788" s="1">
         <v>45890</v>
@@ -35817,7 +35810,7 @@
         <v>43</v>
       </c>
       <c r="B789" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C789" s="1">
         <v>46020</v>
@@ -35899,7 +35892,7 @@
         <v>26</v>
       </c>
       <c r="B791" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C791" s="1">
         <v>45827</v>
@@ -35940,7 +35933,7 @@
         <v>43</v>
       </c>
       <c r="B792" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C792" s="1">
         <v>45895</v>
@@ -35981,7 +35974,7 @@
         <v>79</v>
       </c>
       <c r="B793" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C793" s="1">
         <v>45649</v>
@@ -36022,7 +36015,7 @@
         <v>104</v>
       </c>
       <c r="B794" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C794" s="1">
         <v>45912</v>
@@ -36063,7 +36056,7 @@
         <v>37</v>
       </c>
       <c r="B795" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C795" s="1">
         <v>45688</v>
@@ -36104,7 +36097,7 @@
         <v>37</v>
       </c>
       <c r="B796" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C796" s="1">
         <v>46016</v>
@@ -36145,7 +36138,7 @@
         <v>63</v>
       </c>
       <c r="B797" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C797" s="1">
         <v>45882</v>
@@ -36186,7 +36179,7 @@
         <v>55</v>
       </c>
       <c r="B798" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C798" s="1">
         <v>45573</v>
@@ -36227,7 +36220,7 @@
         <v>104</v>
       </c>
       <c r="B799" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C799" s="1">
         <v>45795</v>
@@ -36268,7 +36261,7 @@
         <v>13</v>
       </c>
       <c r="B800" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C800" s="1">
         <v>45409</v>
@@ -36309,7 +36302,7 @@
         <v>26</v>
       </c>
       <c r="B801" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C801" s="1">
         <v>45986</v>
@@ -36350,7 +36343,7 @@
         <v>79</v>
       </c>
       <c r="B802" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C802" s="1">
         <v>45437</v>
@@ -36391,7 +36384,7 @@
         <v>71</v>
       </c>
       <c r="B803" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C803" s="1">
         <v>45796</v>
@@ -36432,7 +36425,7 @@
         <v>37</v>
       </c>
       <c r="B804" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C804" s="1">
         <v>45321</v>
@@ -36473,7 +36466,7 @@
         <v>43</v>
       </c>
       <c r="B805" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C805" s="1">
         <v>45873</v>
@@ -36514,7 +36507,7 @@
         <v>55</v>
       </c>
       <c r="B806" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C806" s="1">
         <v>45842</v>
@@ -36555,7 +36548,7 @@
         <v>26</v>
       </c>
       <c r="B807" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C807" s="1">
         <v>45292</v>
@@ -36596,7 +36589,7 @@
         <v>63</v>
       </c>
       <c r="B808" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C808" s="1">
         <v>45580</v>
@@ -36637,7 +36630,7 @@
         <v>43</v>
       </c>
       <c r="B809" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C809" s="1">
         <v>45734</v>
@@ -36678,7 +36671,7 @@
         <v>60</v>
       </c>
       <c r="B810" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C810" s="1">
         <v>45543</v>
@@ -36719,7 +36712,7 @@
         <v>123</v>
       </c>
       <c r="B811" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C811" s="1">
         <v>45296</v>
@@ -36760,7 +36753,7 @@
         <v>37</v>
       </c>
       <c r="B812" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C812" s="1">
         <v>45843</v>
@@ -36801,7 +36794,7 @@
         <v>84</v>
       </c>
       <c r="B813" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C813" s="1">
         <v>45473</v>
@@ -36842,7 +36835,7 @@
         <v>13</v>
       </c>
       <c r="B814" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C814" s="1">
         <v>45488</v>
@@ -36883,7 +36876,7 @@
         <v>84</v>
       </c>
       <c r="B815" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C815" s="1">
         <v>45579</v>
@@ -36924,7 +36917,7 @@
         <v>13</v>
       </c>
       <c r="B816" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C816" s="1">
         <v>45797</v>
@@ -36965,7 +36958,7 @@
         <v>43</v>
       </c>
       <c r="B817" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C817" s="1">
         <v>45422</v>
@@ -37006,7 +36999,7 @@
         <v>123</v>
       </c>
       <c r="B818" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C818" s="1">
         <v>45921</v>
@@ -37047,7 +37040,7 @@
         <v>52</v>
       </c>
       <c r="B819" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C819" s="1">
         <v>45708</v>
@@ -37088,7 +37081,7 @@
         <v>71</v>
       </c>
       <c r="B820" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C820" s="1">
         <v>45576</v>
@@ -37129,7 +37122,7 @@
         <v>123</v>
       </c>
       <c r="B821" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C821" s="1">
         <v>45998</v>
@@ -37170,7 +37163,7 @@
         <v>123</v>
       </c>
       <c r="B822" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C822" s="1">
         <v>45734</v>
@@ -37211,7 +37204,7 @@
         <v>52</v>
       </c>
       <c r="B823" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C823" s="1">
         <v>45633</v>
@@ -37252,7 +37245,7 @@
         <v>79</v>
       </c>
       <c r="B824" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C824" s="1">
         <v>45354</v>
@@ -37293,7 +37286,7 @@
         <v>32</v>
       </c>
       <c r="B825" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C825" s="1">
         <v>45917</v>
@@ -37334,7 +37327,7 @@
         <v>79</v>
       </c>
       <c r="B826" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C826" s="1">
         <v>45530</v>
@@ -37375,7 +37368,7 @@
         <v>79</v>
       </c>
       <c r="B827" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C827" s="1">
         <v>45958</v>
@@ -37416,7 +37409,7 @@
         <v>37</v>
       </c>
       <c r="B828" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C828" s="1">
         <v>45878</v>
@@ -37457,7 +37450,7 @@
         <v>71</v>
       </c>
       <c r="B829" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C829" s="1">
         <v>45337</v>
@@ -37498,7 +37491,7 @@
         <v>26</v>
       </c>
       <c r="B830" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C830" s="1">
         <v>45441</v>
@@ -37580,7 +37573,7 @@
         <v>37</v>
       </c>
       <c r="B832" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C832" s="1">
         <v>45485</v>
@@ -37621,7 +37614,7 @@
         <v>26</v>
       </c>
       <c r="B833" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C833" s="1">
         <v>45628</v>
@@ -37662,7 +37655,7 @@
         <v>71</v>
       </c>
       <c r="B834" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C834" s="1">
         <v>45930</v>
@@ -37703,7 +37696,7 @@
         <v>123</v>
       </c>
       <c r="B835" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C835" s="1">
         <v>45302</v>
@@ -37744,7 +37737,7 @@
         <v>84</v>
       </c>
       <c r="B836" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C836" s="1">
         <v>45322</v>
@@ -37785,7 +37778,7 @@
         <v>71</v>
       </c>
       <c r="B837" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C837" s="1">
         <v>45492</v>
@@ -37826,7 +37819,7 @@
         <v>104</v>
       </c>
       <c r="B838" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C838" s="1">
         <v>45638</v>
@@ -37867,7 +37860,7 @@
         <v>129</v>
       </c>
       <c r="B839" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C839" s="1">
         <v>45413</v>
@@ -37908,7 +37901,7 @@
         <v>129</v>
       </c>
       <c r="B840" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C840" s="1">
         <v>45339</v>
@@ -37949,7 +37942,7 @@
         <v>13</v>
       </c>
       <c r="B841" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C841" s="1">
         <v>45812</v>
@@ -37990,7 +37983,7 @@
         <v>55</v>
       </c>
       <c r="B842" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C842" s="1">
         <v>45689</v>
@@ -38031,7 +38024,7 @@
         <v>142</v>
       </c>
       <c r="B843" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C843" s="1">
         <v>45777</v>
@@ -38072,7 +38065,7 @@
         <v>60</v>
       </c>
       <c r="B844" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C844" s="1">
         <v>45697</v>
@@ -38113,7 +38106,7 @@
         <v>37</v>
       </c>
       <c r="B845" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C845" s="1">
         <v>45378</v>
@@ -38154,7 +38147,7 @@
         <v>52</v>
       </c>
       <c r="B846" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C846" s="1">
         <v>45753</v>
@@ -38195,7 +38188,7 @@
         <v>55</v>
       </c>
       <c r="B847" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C847" s="1">
         <v>45531</v>
@@ -38236,7 +38229,7 @@
         <v>13</v>
       </c>
       <c r="B848" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C848" s="1">
         <v>45392</v>
@@ -38277,7 +38270,7 @@
         <v>13</v>
       </c>
       <c r="B849" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C849" s="1">
         <v>45991</v>
@@ -38318,7 +38311,7 @@
         <v>13</v>
       </c>
       <c r="B850" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C850" s="1">
         <v>45598</v>
@@ -38359,7 +38352,7 @@
         <v>142</v>
       </c>
       <c r="B851" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C851" s="1">
         <v>45444</v>
@@ -38400,7 +38393,7 @@
         <v>60</v>
       </c>
       <c r="B852" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C852" s="1">
         <v>45640</v>
@@ -38441,7 +38434,7 @@
         <v>60</v>
       </c>
       <c r="B853" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C853" s="1">
         <v>45863</v>
@@ -38482,7 +38475,7 @@
         <v>142</v>
       </c>
       <c r="B854" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C854" s="1">
         <v>45639</v>
@@ -38523,7 +38516,7 @@
         <v>123</v>
       </c>
       <c r="B855" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C855" s="1">
         <v>45434</v>
@@ -38564,7 +38557,7 @@
         <v>63</v>
       </c>
       <c r="B856" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C856" s="1">
         <v>45357</v>
@@ -38605,7 +38598,7 @@
         <v>37</v>
       </c>
       <c r="B857" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C857" s="1">
         <v>45398</v>
@@ -38646,7 +38639,7 @@
         <v>26</v>
       </c>
       <c r="B858" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C858" s="1">
         <v>45530</v>
@@ -38687,7 +38680,7 @@
         <v>129</v>
       </c>
       <c r="B859" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C859" s="1">
         <v>45452</v>
@@ -38728,7 +38721,7 @@
         <v>43</v>
       </c>
       <c r="B860" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C860" s="1">
         <v>45609</v>
@@ -38769,7 +38762,7 @@
         <v>60</v>
       </c>
       <c r="B861" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C861" s="1">
         <v>45498</v>
@@ -38810,7 +38803,7 @@
         <v>52</v>
       </c>
       <c r="B862" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C862" s="1">
         <v>45763</v>
@@ -38851,7 +38844,7 @@
         <v>26</v>
       </c>
       <c r="B863" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C863" s="1">
         <v>45919</v>
@@ -38892,7 +38885,7 @@
         <v>55</v>
       </c>
       <c r="B864" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C864" s="1">
         <v>45694</v>
@@ -38933,7 +38926,7 @@
         <v>63</v>
       </c>
       <c r="B865" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C865" s="1">
         <v>45713</v>
@@ -38974,7 +38967,7 @@
         <v>129</v>
       </c>
       <c r="B866" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C866" s="1">
         <v>45460</v>
@@ -39015,7 +39008,7 @@
         <v>104</v>
       </c>
       <c r="B867" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C867" s="1">
         <v>45700</v>
@@ -39056,7 +39049,7 @@
         <v>60</v>
       </c>
       <c r="B868" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C868" s="1">
         <v>45764</v>
@@ -39097,7 +39090,7 @@
         <v>55</v>
       </c>
       <c r="B869" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C869" s="1">
         <v>45310</v>
@@ -39138,7 +39131,7 @@
         <v>123</v>
       </c>
       <c r="B870" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C870" s="1">
         <v>45449</v>
@@ -39179,7 +39172,7 @@
         <v>60</v>
       </c>
       <c r="B871" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C871" s="1">
         <v>45942</v>
@@ -39220,7 +39213,7 @@
         <v>63</v>
       </c>
       <c r="B872" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C872" s="1">
         <v>45675</v>
@@ -39261,7 +39254,7 @@
         <v>37</v>
       </c>
       <c r="B873" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C873" s="1">
         <v>45390</v>
@@ -39302,7 +39295,7 @@
         <v>63</v>
       </c>
       <c r="B874" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C874" s="1">
         <v>45846</v>
@@ -39343,7 +39336,7 @@
         <v>104</v>
       </c>
       <c r="B875" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C875" s="1">
         <v>45304</v>
@@ -39384,7 +39377,7 @@
         <v>84</v>
       </c>
       <c r="B876" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C876" s="1">
         <v>45360</v>
@@ -39425,7 +39418,7 @@
         <v>55</v>
       </c>
       <c r="B877" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C877" s="1">
         <v>45389</v>
@@ -39466,7 +39459,7 @@
         <v>55</v>
       </c>
       <c r="B878" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C878" s="1">
         <v>45974</v>
@@ -39507,7 +39500,7 @@
         <v>71</v>
       </c>
       <c r="B879" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C879" s="1">
         <v>45893</v>
@@ -39548,7 +39541,7 @@
         <v>71</v>
       </c>
       <c r="B880" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C880" s="1">
         <v>45353</v>
@@ -39589,7 +39582,7 @@
         <v>71</v>
       </c>
       <c r="B881" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C881" s="1">
         <v>45628</v>
@@ -39630,7 +39623,7 @@
         <v>123</v>
       </c>
       <c r="B882" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C882" s="1">
         <v>45631</v>
@@ -39671,7 +39664,7 @@
         <v>71</v>
       </c>
       <c r="B883" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C883" s="1">
         <v>45825</v>
@@ -39712,7 +39705,7 @@
         <v>32</v>
       </c>
       <c r="B884" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C884" s="1">
         <v>45501</v>
@@ -39753,7 +39746,7 @@
         <v>37</v>
       </c>
       <c r="B885" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C885" s="1">
         <v>45770</v>
@@ -39794,7 +39787,7 @@
         <v>26</v>
       </c>
       <c r="B886" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C886" s="1">
         <v>45942</v>
@@ -39835,7 +39828,7 @@
         <v>142</v>
       </c>
       <c r="B887" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C887" s="1">
         <v>45724</v>
@@ -39876,7 +39869,7 @@
         <v>123</v>
       </c>
       <c r="B888" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C888" s="1">
         <v>45729</v>
@@ -39917,7 +39910,7 @@
         <v>60</v>
       </c>
       <c r="B889" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C889" s="1">
         <v>45756</v>
@@ -39999,7 +39992,7 @@
         <v>104</v>
       </c>
       <c r="B891" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C891" s="1">
         <v>45685</v>
@@ -40040,7 +40033,7 @@
         <v>104</v>
       </c>
       <c r="B892" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C892" s="1">
         <v>45490</v>
@@ -40081,7 +40074,7 @@
         <v>32</v>
       </c>
       <c r="B893" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C893" s="1">
         <v>45726</v>
@@ -40122,7 +40115,7 @@
         <v>43</v>
       </c>
       <c r="B894" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C894" s="1">
         <v>45911</v>
@@ -40163,7 +40156,7 @@
         <v>123</v>
       </c>
       <c r="B895" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C895" s="1">
         <v>45386</v>
@@ -40204,7 +40197,7 @@
         <v>129</v>
       </c>
       <c r="B896" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C896" s="1">
         <v>45729</v>
@@ -40245,7 +40238,7 @@
         <v>37</v>
       </c>
       <c r="B897" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C897" s="1">
         <v>45943</v>
@@ -40286,7 +40279,7 @@
         <v>26</v>
       </c>
       <c r="B898" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C898" s="1">
         <v>45464</v>
@@ -40327,7 +40320,7 @@
         <v>129</v>
       </c>
       <c r="B899" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C899" s="1">
         <v>45472</v>
@@ -40368,7 +40361,7 @@
         <v>60</v>
       </c>
       <c r="B900" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C900" s="1">
         <v>45482</v>
@@ -40409,7 +40402,7 @@
         <v>60</v>
       </c>
       <c r="B901" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C901" s="1">
         <v>45943</v>
@@ -40450,7 +40443,7 @@
         <v>71</v>
       </c>
       <c r="B902" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C902" s="1">
         <v>45788</v>
@@ -40491,7 +40484,7 @@
         <v>79</v>
       </c>
       <c r="B903" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C903" s="1">
         <v>45826</v>
@@ -40532,7 +40525,7 @@
         <v>142</v>
       </c>
       <c r="B904" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C904" s="1">
         <v>45910</v>
@@ -40573,7 +40566,7 @@
         <v>104</v>
       </c>
       <c r="B905" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C905" s="1">
         <v>45917</v>
@@ -40614,7 +40607,7 @@
         <v>43</v>
       </c>
       <c r="B906" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C906" s="1">
         <v>45908</v>
@@ -40655,7 +40648,7 @@
         <v>129</v>
       </c>
       <c r="B907" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C907" s="1">
         <v>45295</v>
@@ -40696,7 +40689,7 @@
         <v>71</v>
       </c>
       <c r="B908" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C908" s="1">
         <v>45701</v>
@@ -40737,7 +40730,7 @@
         <v>104</v>
       </c>
       <c r="B909" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C909" s="1">
         <v>45913</v>
@@ -40778,7 +40771,7 @@
         <v>32</v>
       </c>
       <c r="B910" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C910" s="1">
         <v>45801</v>
@@ -40819,7 +40812,7 @@
         <v>79</v>
       </c>
       <c r="B911" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C911" s="1">
         <v>45970</v>
@@ -40860,7 +40853,7 @@
         <v>79</v>
       </c>
       <c r="B912" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C912" s="1">
         <v>45321</v>
@@ -40901,7 +40894,7 @@
         <v>43</v>
       </c>
       <c r="B913" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C913" s="1">
         <v>45940</v>
@@ -40942,7 +40935,7 @@
         <v>37</v>
       </c>
       <c r="B914" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C914" s="1">
         <v>45678</v>
@@ -40983,7 +40976,7 @@
         <v>37</v>
       </c>
       <c r="B915" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C915" s="1">
         <v>45383</v>
@@ -41024,7 +41017,7 @@
         <v>123</v>
       </c>
       <c r="B916" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C916" s="1">
         <v>45355</v>
@@ -41065,7 +41058,7 @@
         <v>71</v>
       </c>
       <c r="B917" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C917" s="1">
         <v>45696</v>
@@ -41106,7 +41099,7 @@
         <v>142</v>
       </c>
       <c r="B918" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C918" s="1">
         <v>45442</v>
@@ -41147,7 +41140,7 @@
         <v>13</v>
       </c>
       <c r="B919" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C919" s="1">
         <v>45938</v>
@@ -41229,7 +41222,7 @@
         <v>142</v>
       </c>
       <c r="B921" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C921" s="1">
         <v>45692</v>
@@ -41270,7 +41263,7 @@
         <v>104</v>
       </c>
       <c r="B922" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C922" s="1">
         <v>45426</v>
@@ -41311,7 +41304,7 @@
         <v>43</v>
       </c>
       <c r="B923" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C923" s="1">
         <v>46004</v>
@@ -41352,7 +41345,7 @@
         <v>84</v>
       </c>
       <c r="B924" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C924" s="1">
         <v>45986</v>
@@ -41393,7 +41386,7 @@
         <v>55</v>
       </c>
       <c r="B925" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C925" s="1">
         <v>45412</v>
@@ -41434,7 +41427,7 @@
         <v>32</v>
       </c>
       <c r="B926" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C926" s="1">
         <v>45538</v>
@@ -41475,7 +41468,7 @@
         <v>60</v>
       </c>
       <c r="B927" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C927" s="1">
         <v>45573</v>
@@ -41516,7 +41509,7 @@
         <v>71</v>
       </c>
       <c r="B928" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C928" s="1">
         <v>45892</v>
@@ -41557,7 +41550,7 @@
         <v>104</v>
       </c>
       <c r="B929" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C929" s="1">
         <v>45952</v>
@@ -41598,7 +41591,7 @@
         <v>55</v>
       </c>
       <c r="B930" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C930" s="1">
         <v>46009</v>
@@ -41639,7 +41632,7 @@
         <v>79</v>
       </c>
       <c r="B931" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C931" s="1">
         <v>45966</v>
@@ -41680,7 +41673,7 @@
         <v>79</v>
       </c>
       <c r="B932" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C932" s="1">
         <v>45423</v>
@@ -41721,7 +41714,7 @@
         <v>37</v>
       </c>
       <c r="B933" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C933" s="1">
         <v>45810</v>
@@ -41762,7 +41755,7 @@
         <v>26</v>
       </c>
       <c r="B934" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C934" s="1">
         <v>45823</v>
@@ -41803,7 +41796,7 @@
         <v>63</v>
       </c>
       <c r="B935" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C935" s="1">
         <v>45970</v>
@@ -41844,7 +41837,7 @@
         <v>63</v>
       </c>
       <c r="B936" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C936" s="1">
         <v>45576</v>
@@ -41885,7 +41878,7 @@
         <v>104</v>
       </c>
       <c r="B937" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C937" s="1">
         <v>45377</v>
@@ -41926,7 +41919,7 @@
         <v>63</v>
       </c>
       <c r="B938" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C938" s="1">
         <v>45869</v>
@@ -42008,7 +42001,7 @@
         <v>52</v>
       </c>
       <c r="B940" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C940" s="1">
         <v>45663</v>
@@ -42049,7 +42042,7 @@
         <v>104</v>
       </c>
       <c r="B941" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C941" s="1">
         <v>45418</v>
@@ -42090,7 +42083,7 @@
         <v>84</v>
       </c>
       <c r="B942" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C942" s="1">
         <v>45856</v>
@@ -42131,7 +42124,7 @@
         <v>84</v>
       </c>
       <c r="B943" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C943" s="1">
         <v>45856</v>
@@ -42172,7 +42165,7 @@
         <v>43</v>
       </c>
       <c r="B944" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C944" s="1">
         <v>45679</v>
@@ -42213,7 +42206,7 @@
         <v>60</v>
       </c>
       <c r="B945" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C945" s="1">
         <v>45741</v>
@@ -42254,7 +42247,7 @@
         <v>26</v>
       </c>
       <c r="B946" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C946" s="1">
         <v>45604</v>
@@ -42295,7 +42288,7 @@
         <v>55</v>
       </c>
       <c r="B947" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C947" s="1">
         <v>45378</v>
@@ -42336,7 +42329,7 @@
         <v>142</v>
       </c>
       <c r="B948" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C948" s="1">
         <v>45819</v>
@@ -42377,7 +42370,7 @@
         <v>129</v>
       </c>
       <c r="B949" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C949" s="1">
         <v>45645</v>
@@ -42418,7 +42411,7 @@
         <v>71</v>
       </c>
       <c r="B950" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C950" s="1">
         <v>45368</v>
@@ -42459,7 +42452,7 @@
         <v>84</v>
       </c>
       <c r="B951" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C951" s="1">
         <v>45638</v>
@@ -42500,7 +42493,7 @@
         <v>123</v>
       </c>
       <c r="B952" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C952" s="1">
         <v>45514</v>
@@ -42541,7 +42534,7 @@
         <v>32</v>
       </c>
       <c r="B953" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C953" s="1">
         <v>45298</v>
@@ -42582,7 +42575,7 @@
         <v>104</v>
       </c>
       <c r="B954" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C954" s="1">
         <v>45301</v>
@@ -42623,7 +42616,7 @@
         <v>79</v>
       </c>
       <c r="B955" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C955" s="1">
         <v>45299</v>
@@ -42664,7 +42657,7 @@
         <v>13</v>
       </c>
       <c r="B956" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C956" s="1">
         <v>45741</v>
@@ -42705,7 +42698,7 @@
         <v>79</v>
       </c>
       <c r="B957" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C957" s="1">
         <v>45583</v>
@@ -42746,7 +42739,7 @@
         <v>142</v>
       </c>
       <c r="B958" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C958" s="1">
         <v>45413</v>
@@ -42787,7 +42780,7 @@
         <v>104</v>
       </c>
       <c r="B959" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C959" s="1">
         <v>45404</v>
@@ -42828,7 +42821,7 @@
         <v>32</v>
       </c>
       <c r="B960" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C960" s="1">
         <v>45731</v>
@@ -42869,7 +42862,7 @@
         <v>71</v>
       </c>
       <c r="B961" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C961" s="1">
         <v>45815</v>
@@ -42910,7 +42903,7 @@
         <v>63</v>
       </c>
       <c r="B962" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C962" s="1">
         <v>46015</v>
@@ -42951,7 +42944,7 @@
         <v>71</v>
       </c>
       <c r="B963" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C963" s="1">
         <v>45427</v>
@@ -42992,7 +42985,7 @@
         <v>37</v>
       </c>
       <c r="B964" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C964" s="1">
         <v>45681</v>
@@ -43033,7 +43026,7 @@
         <v>129</v>
       </c>
       <c r="B965" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C965" s="1">
         <v>45603</v>
@@ -43074,7 +43067,7 @@
         <v>32</v>
       </c>
       <c r="B966" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C966" s="1">
         <v>45333</v>
@@ -43115,7 +43108,7 @@
         <v>79</v>
       </c>
       <c r="B967" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C967" s="1">
         <v>45481</v>
@@ -43156,7 +43149,7 @@
         <v>43</v>
       </c>
       <c r="B968" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C968" s="1">
         <v>45661</v>
@@ -43197,7 +43190,7 @@
         <v>104</v>
       </c>
       <c r="B969" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C969" s="1">
         <v>45400</v>
@@ -43238,7 +43231,7 @@
         <v>63</v>
       </c>
       <c r="B970" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C970" s="1">
         <v>45393</v>
@@ -43279,7 +43272,7 @@
         <v>43</v>
       </c>
       <c r="B971" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C971" s="1">
         <v>45422</v>
@@ -43320,7 +43313,7 @@
         <v>84</v>
       </c>
       <c r="B972" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C972" s="1">
         <v>45751</v>
@@ -43361,7 +43354,7 @@
         <v>55</v>
       </c>
       <c r="B973" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C973" s="1">
         <v>46005</v>
@@ -43402,7 +43395,7 @@
         <v>142</v>
       </c>
       <c r="B974" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C974" s="1">
         <v>45817</v>
@@ -43443,7 +43436,7 @@
         <v>13</v>
       </c>
       <c r="B975" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C975" s="1">
         <v>45480</v>
@@ -43525,7 +43518,7 @@
         <v>71</v>
       </c>
       <c r="B977" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C977" s="1">
         <v>45838</v>
@@ -43566,7 +43559,7 @@
         <v>32</v>
       </c>
       <c r="B978" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C978" s="1">
         <v>45507</v>
@@ -43607,7 +43600,7 @@
         <v>13</v>
       </c>
       <c r="B979" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C979" s="1">
         <v>45710</v>
@@ -43648,7 +43641,7 @@
         <v>13</v>
       </c>
       <c r="B980" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C980" s="1">
         <v>45554</v>
@@ -43689,7 +43682,7 @@
         <v>63</v>
       </c>
       <c r="B981" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C981" s="1">
         <v>45517</v>
@@ -43730,7 +43723,7 @@
         <v>60</v>
       </c>
       <c r="B982" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C982" s="1">
         <v>45736</v>
@@ -43771,7 +43764,7 @@
         <v>63</v>
       </c>
       <c r="B983" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C983" s="1">
         <v>45476</v>
@@ -43853,7 +43846,7 @@
         <v>43</v>
       </c>
       <c r="B985" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C985" s="1">
         <v>45909</v>
@@ -43894,7 +43887,7 @@
         <v>43</v>
       </c>
       <c r="B986" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C986" s="1">
         <v>45377</v>
@@ -43935,7 +43928,7 @@
         <v>52</v>
       </c>
       <c r="B987" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C987" s="1">
         <v>45499</v>
@@ -44017,7 +44010,7 @@
         <v>79</v>
       </c>
       <c r="B989" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C989" s="1">
         <v>45595</v>
@@ -44058,7 +44051,7 @@
         <v>129</v>
       </c>
       <c r="B990" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C990" s="1">
         <v>45442</v>
@@ -44099,7 +44092,7 @@
         <v>142</v>
       </c>
       <c r="B991" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C991" s="1">
         <v>45404</v>
@@ -44140,7 +44133,7 @@
         <v>32</v>
       </c>
       <c r="B992" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C992" s="1">
         <v>45474</v>
@@ -44181,7 +44174,7 @@
         <v>26</v>
       </c>
       <c r="B993" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C993" s="1">
         <v>45398</v>
@@ -44222,7 +44215,7 @@
         <v>123</v>
       </c>
       <c r="B994" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C994" s="1">
         <v>45963</v>
@@ -44263,7 +44256,7 @@
         <v>37</v>
       </c>
       <c r="B995" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C995" s="1">
         <v>45883</v>
@@ -44345,7 +44338,7 @@
         <v>104</v>
       </c>
       <c r="B997" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C997" s="1">
         <v>45854</v>
@@ -44427,7 +44420,7 @@
         <v>142</v>
       </c>
       <c r="B999" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C999" s="1">
         <v>45404</v>
@@ -44468,7 +44461,7 @@
         <v>129</v>
       </c>
       <c r="B1000" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C1000" s="1">
         <v>45507</v>
@@ -44501,7 +44494,7 @@
         <v>0.27010000000000001</v>
       </c>
       <c r="M1000" t="s">
-        <v>291</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1001" spans="1:13" x14ac:dyDescent="0.3">
@@ -44509,7 +44502,7 @@
         <v>26</v>
       </c>
       <c r="B1001" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C1001" s="1">
         <v>45986</v>
@@ -44550,7 +44543,7 @@
         <v>79</v>
       </c>
       <c r="B1002" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C1002" s="1">
         <v>45437</v>
@@ -44591,7 +44584,7 @@
         <v>71</v>
       </c>
       <c r="B1003" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C1003" s="1">
         <v>45796</v>
@@ -44632,7 +44625,7 @@
         <v>37</v>
       </c>
       <c r="B1004" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C1004" s="1">
         <v>45321</v>
@@ -44673,7 +44666,7 @@
         <v>43</v>
       </c>
       <c r="B1005" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C1005" s="1">
         <v>45873</v>
@@ -44714,7 +44707,7 @@
         <v>55</v>
       </c>
       <c r="B1006" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C1006" s="1">
         <v>45842</v>
@@ -44755,7 +44748,7 @@
         <v>26</v>
       </c>
       <c r="B1007" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C1007" s="1">
         <v>45292</v>
@@ -44796,7 +44789,7 @@
         <v>63</v>
       </c>
       <c r="B1008" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C1008" s="1">
         <v>45580</v>
@@ -44837,7 +44830,7 @@
         <v>43</v>
       </c>
       <c r="B1009" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C1009" s="1">
         <v>45734</v>
@@ -44878,7 +44871,7 @@
         <v>60</v>
       </c>
       <c r="B1010" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="C1010" s="1">
         <v>45543</v>
@@ -44919,7 +44912,7 @@
         <v>123</v>
       </c>
       <c r="B1011" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C1011" s="1">
         <v>45296</v>
@@ -44960,7 +44953,7 @@
         <v>37</v>
       </c>
       <c r="B1012" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C1012" s="1">
         <v>45843</v>
@@ -45001,7 +44994,7 @@
         <v>84</v>
       </c>
       <c r="B1013" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C1013" s="1">
         <v>45473</v>
@@ -45042,7 +45035,7 @@
         <v>13</v>
       </c>
       <c r="B1014" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C1014" s="1">
         <v>45488</v>
@@ -45083,7 +45076,7 @@
         <v>84</v>
       </c>
       <c r="B1015" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C1015" s="1">
         <v>45579</v>
@@ -45124,7 +45117,7 @@
         <v>13</v>
       </c>
       <c r="B1016" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C1016" s="1">
         <v>45797</v>
@@ -45165,7 +45158,7 @@
         <v>43</v>
       </c>
       <c r="B1017" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C1017" s="1">
         <v>45422</v>
@@ -45206,7 +45199,7 @@
         <v>123</v>
       </c>
       <c r="B1018" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C1018" s="1">
         <v>45921</v>
@@ -45247,7 +45240,7 @@
         <v>52</v>
       </c>
       <c r="B1019" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C1019" s="1">
         <v>45708</v>
@@ -45288,7 +45281,7 @@
         <v>71</v>
       </c>
       <c r="B1020" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="C1020" s="1">
         <v>45576</v>
@@ -45329,7 +45322,7 @@
         <v>123</v>
       </c>
       <c r="B1021" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="C1021" s="1">
         <v>45998</v>
@@ -45370,7 +45363,7 @@
         <v>123</v>
       </c>
       <c r="B1022" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="C1022" s="1">
         <v>45734</v>
@@ -45411,7 +45404,7 @@
         <v>52</v>
       </c>
       <c r="B1023" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C1023" s="1">
         <v>45633</v>
@@ -45452,7 +45445,7 @@
         <v>79</v>
       </c>
       <c r="B1024" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="C1024" s="1">
         <v>45354</v>
@@ -45493,7 +45486,7 @@
         <v>32</v>
       </c>
       <c r="B1025" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="C1025" s="1">
         <v>45917</v>
@@ -45534,7 +45527,7 @@
         <v>79</v>
       </c>
       <c r="B1026" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C1026" s="1">
         <v>45530</v>
@@ -45575,7 +45568,7 @@
         <v>79</v>
       </c>
       <c r="B1027" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C1027" s="1">
         <v>45958</v>
@@ -45616,7 +45609,7 @@
         <v>37</v>
       </c>
       <c r="B1028" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C1028" s="1">
         <v>45878</v>
@@ -45657,7 +45650,7 @@
         <v>71</v>
       </c>
       <c r="B1029" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C1029" s="1">
         <v>45337</v>
@@ -45698,7 +45691,7 @@
         <v>26</v>
       </c>
       <c r="B1030" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="C1030" s="1">
         <v>45441</v>
@@ -45780,7 +45773,7 @@
         <v>37</v>
       </c>
       <c r="B1032" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C1032" s="1">
         <v>45485</v>
@@ -45821,7 +45814,7 @@
         <v>26</v>
       </c>
       <c r="B1033" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C1033" s="1">
         <v>45628</v>
@@ -45862,7 +45855,7 @@
         <v>71</v>
       </c>
       <c r="B1034" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C1034" s="1">
         <v>45930</v>
@@ -45903,7 +45896,7 @@
         <v>123</v>
       </c>
       <c r="B1035" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="C1035" s="1">
         <v>45302</v>
@@ -45944,7 +45937,7 @@
         <v>84</v>
       </c>
       <c r="B1036" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C1036" s="1">
         <v>45322</v>
@@ -45985,7 +45978,7 @@
         <v>71</v>
       </c>
       <c r="B1037" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C1037" s="1">
         <v>45492</v>
@@ -46026,7 +46019,7 @@
         <v>104</v>
       </c>
       <c r="B1038" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C1038" s="1">
         <v>45638</v>
@@ -46067,7 +46060,7 @@
         <v>129</v>
       </c>
       <c r="B1039" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C1039" s="1">
         <v>45413</v>
@@ -46108,7 +46101,7 @@
         <v>129</v>
       </c>
       <c r="B1040" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C1040" s="1">
         <v>45339</v>
@@ -46149,7 +46142,7 @@
         <v>13</v>
       </c>
       <c r="B1041" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C1041" s="1">
         <v>45812</v>
@@ -46190,7 +46183,7 @@
         <v>55</v>
       </c>
       <c r="B1042" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C1042" s="1">
         <v>45689</v>
@@ -46231,7 +46224,7 @@
         <v>142</v>
       </c>
       <c r="B1043" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C1043" s="1">
         <v>45777</v>
@@ -46272,7 +46265,7 @@
         <v>60</v>
       </c>
       <c r="B1044" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C1044" s="1">
         <v>45697</v>
@@ -46313,7 +46306,7 @@
         <v>37</v>
       </c>
       <c r="B1045" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C1045" s="1">
         <v>45378</v>
@@ -46354,7 +46347,7 @@
         <v>52</v>
       </c>
       <c r="B1046" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C1046" s="1">
         <v>45753</v>
@@ -46395,7 +46388,7 @@
         <v>55</v>
       </c>
       <c r="B1047" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C1047" s="1">
         <v>45531</v>
@@ -46436,7 +46429,7 @@
         <v>13</v>
       </c>
       <c r="B1048" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C1048" s="1">
         <v>45392</v>
@@ -46477,7 +46470,7 @@
         <v>13</v>
       </c>
       <c r="B1049" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C1049" s="1">
         <v>45991</v>
@@ -46518,7 +46511,7 @@
         <v>13</v>
       </c>
       <c r="B1050" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C1050" s="1">
         <v>45598</v>
@@ -46559,7 +46552,7 @@
         <v>142</v>
       </c>
       <c r="B1051" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C1051" s="1">
         <v>45444</v>
@@ -46600,7 +46593,7 @@
         <v>60</v>
       </c>
       <c r="B1052" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C1052" s="1">
         <v>45640</v>
@@ -46641,7 +46634,7 @@
         <v>60</v>
       </c>
       <c r="B1053" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="C1053" s="1">
         <v>45863</v>
@@ -46682,7 +46675,7 @@
         <v>142</v>
       </c>
       <c r="B1054" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C1054" s="1">
         <v>45639</v>
@@ -46723,7 +46716,7 @@
         <v>123</v>
       </c>
       <c r="B1055" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C1055" s="1">
         <v>45434</v>
@@ -46764,7 +46757,7 @@
         <v>63</v>
       </c>
       <c r="B1056" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C1056" s="1">
         <v>45357</v>
@@ -46805,7 +46798,7 @@
         <v>37</v>
       </c>
       <c r="B1057" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C1057" s="1">
         <v>45398</v>
@@ -46846,7 +46839,7 @@
         <v>26</v>
       </c>
       <c r="B1058" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C1058" s="1">
         <v>45530</v>
@@ -46887,7 +46880,7 @@
         <v>129</v>
       </c>
       <c r="B1059" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C1059" s="1">
         <v>45452</v>
@@ -46928,7 +46921,7 @@
         <v>43</v>
       </c>
       <c r="B1060" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C1060" s="1">
         <v>45609</v>
@@ -46969,7 +46962,7 @@
         <v>60</v>
       </c>
       <c r="B1061" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C1061" s="1">
         <v>45498</v>
@@ -47010,7 +47003,7 @@
         <v>52</v>
       </c>
       <c r="B1062" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C1062" s="1">
         <v>45763</v>
@@ -47051,7 +47044,7 @@
         <v>26</v>
       </c>
       <c r="B1063" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C1063" s="1">
         <v>45919</v>
@@ -47092,7 +47085,7 @@
         <v>55</v>
       </c>
       <c r="B1064" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C1064" s="1">
         <v>45694</v>
@@ -47133,7 +47126,7 @@
         <v>63</v>
       </c>
       <c r="B1065" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C1065" s="1">
         <v>45713</v>
@@ -47174,7 +47167,7 @@
         <v>129</v>
       </c>
       <c r="B1066" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C1066" s="1">
         <v>45460</v>
@@ -47215,7 +47208,7 @@
         <v>104</v>
       </c>
       <c r="B1067" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C1067" s="1">
         <v>45700</v>
@@ -47256,7 +47249,7 @@
         <v>60</v>
       </c>
       <c r="B1068" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="C1068" s="1">
         <v>45764</v>
@@ -47297,7 +47290,7 @@
         <v>55</v>
       </c>
       <c r="B1069" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C1069" s="1">
         <v>45310</v>
@@ -47338,7 +47331,7 @@
         <v>123</v>
       </c>
       <c r="B1070" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="C1070" s="1">
         <v>45449</v>
@@ -47379,7 +47372,7 @@
         <v>60</v>
       </c>
       <c r="B1071" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C1071" s="1">
         <v>45942</v>
@@ -47420,7 +47413,7 @@
         <v>63</v>
       </c>
       <c r="B1072" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C1072" s="1">
         <v>45675</v>
@@ -47461,7 +47454,7 @@
         <v>37</v>
       </c>
       <c r="B1073" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C1073" s="1">
         <v>45390</v>
@@ -47502,7 +47495,7 @@
         <v>63</v>
       </c>
       <c r="B1074" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C1074" s="1">
         <v>45846</v>
@@ -47543,7 +47536,7 @@
         <v>104</v>
       </c>
       <c r="B1075" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C1075" s="1">
         <v>45304</v>
@@ -47584,7 +47577,7 @@
         <v>84</v>
       </c>
       <c r="B1076" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C1076" s="1">
         <v>45360</v>
@@ -47625,7 +47618,7 @@
         <v>55</v>
       </c>
       <c r="B1077" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C1077" s="1">
         <v>45389</v>
@@ -47666,7 +47659,7 @@
         <v>55</v>
       </c>
       <c r="B1078" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C1078" s="1">
         <v>45974</v>
@@ -47707,7 +47700,7 @@
         <v>71</v>
       </c>
       <c r="B1079" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C1079" s="1">
         <v>45893</v>
@@ -47748,7 +47741,7 @@
         <v>71</v>
       </c>
       <c r="B1080" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C1080" s="1">
         <v>45353</v>
@@ -47789,7 +47782,7 @@
         <v>71</v>
       </c>
       <c r="B1081" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C1081" s="1">
         <v>45628</v>
@@ -47830,7 +47823,7 @@
         <v>123</v>
       </c>
       <c r="B1082" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C1082" s="1">
         <v>45631</v>
@@ -47871,7 +47864,7 @@
         <v>71</v>
       </c>
       <c r="B1083" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C1083" s="1">
         <v>45825</v>
@@ -47912,7 +47905,7 @@
         <v>32</v>
       </c>
       <c r="B1084" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C1084" s="1">
         <v>45501</v>
@@ -47953,7 +47946,7 @@
         <v>37</v>
       </c>
       <c r="B1085" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C1085" s="1">
         <v>45770</v>
@@ -47994,7 +47987,7 @@
         <v>26</v>
       </c>
       <c r="B1086" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C1086" s="1">
         <v>45942</v>
@@ -48035,7 +48028,7 @@
         <v>142</v>
       </c>
       <c r="B1087" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C1087" s="1">
         <v>45724</v>
@@ -48076,7 +48069,7 @@
         <v>123</v>
       </c>
       <c r="B1088" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C1088" s="1">
         <v>45729</v>
@@ -48117,7 +48110,7 @@
         <v>60</v>
       </c>
       <c r="B1089" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C1089" s="1">
         <v>45756</v>
@@ -48199,7 +48192,7 @@
         <v>104</v>
       </c>
       <c r="B1091" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C1091" s="1">
         <v>45685</v>
@@ -48240,7 +48233,7 @@
         <v>104</v>
       </c>
       <c r="B1092" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="C1092" s="1">
         <v>45490</v>
@@ -48281,7 +48274,7 @@
         <v>32</v>
       </c>
       <c r="B1093" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="C1093" s="1">
         <v>45726</v>
@@ -48322,7 +48315,7 @@
         <v>43</v>
       </c>
       <c r="B1094" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="C1094" s="1">
         <v>45911</v>
@@ -48363,7 +48356,7 @@
         <v>123</v>
       </c>
       <c r="B1095" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="C1095" s="1">
         <v>45386</v>
@@ -48404,7 +48397,7 @@
         <v>129</v>
       </c>
       <c r="B1096" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="C1096" s="1">
         <v>45729</v>
@@ -48445,7 +48438,7 @@
         <v>37</v>
       </c>
       <c r="B1097" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C1097" s="1">
         <v>45943</v>
@@ -48486,7 +48479,7 @@
         <v>26</v>
       </c>
       <c r="B1098" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="C1098" s="1">
         <v>45464</v>
@@ -48527,7 +48520,7 @@
         <v>129</v>
       </c>
       <c r="B1099" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="C1099" s="1">
         <v>45472</v>
@@ -48568,7 +48561,7 @@
         <v>60</v>
       </c>
       <c r="B1100" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C1100" s="1">
         <v>45482</v>
@@ -48609,7 +48602,7 @@
         <v>60</v>
       </c>
       <c r="B1101" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C1101" s="1">
         <v>45943</v>
@@ -48650,7 +48643,7 @@
         <v>71</v>
       </c>
       <c r="B1102" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="C1102" s="1">
         <v>45788</v>
@@ -48691,7 +48684,7 @@
         <v>79</v>
       </c>
       <c r="B1103" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C1103" s="1">
         <v>45826</v>
@@ -48732,7 +48725,7 @@
         <v>142</v>
       </c>
       <c r="B1104" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="C1104" s="1">
         <v>45910</v>
@@ -48773,7 +48766,7 @@
         <v>104</v>
       </c>
       <c r="B1105" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C1105" s="1">
         <v>45917</v>
@@ -48814,7 +48807,7 @@
         <v>43</v>
       </c>
       <c r="B1106" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="C1106" s="1">
         <v>45908</v>
@@ -48855,7 +48848,7 @@
         <v>129</v>
       </c>
       <c r="B1107" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C1107" s="1">
         <v>45295</v>
@@ -48896,7 +48889,7 @@
         <v>71</v>
       </c>
       <c r="B1108" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="C1108" s="1">
         <v>45701</v>
@@ -48937,7 +48930,7 @@
         <v>104</v>
       </c>
       <c r="B1109" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C1109" s="1">
         <v>45913</v>
@@ -48978,7 +48971,7 @@
         <v>32</v>
       </c>
       <c r="B1110" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="C1110" s="1">
         <v>45801</v>
@@ -49019,7 +49012,7 @@
         <v>79</v>
       </c>
       <c r="B1111" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="C1111" s="1">
         <v>45970</v>
@@ -49060,7 +49053,7 @@
         <v>79</v>
       </c>
       <c r="B1112" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C1112" s="1">
         <v>45321</v>
@@ -49101,7 +49094,7 @@
         <v>43</v>
       </c>
       <c r="B1113" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C1113" s="1">
         <v>45940</v>
@@ -49142,7 +49135,7 @@
         <v>37</v>
       </c>
       <c r="B1114" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C1114" s="1">
         <v>45678</v>
@@ -49183,7 +49176,7 @@
         <v>37</v>
       </c>
       <c r="B1115" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="C1115" s="1">
         <v>45383</v>
@@ -49224,7 +49217,7 @@
         <v>123</v>
       </c>
       <c r="B1116" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C1116" s="1">
         <v>45355</v>
@@ -49265,7 +49258,7 @@
         <v>71</v>
       </c>
       <c r="B1117" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="C1117" s="1">
         <v>45696</v>
@@ -49306,7 +49299,7 @@
         <v>142</v>
       </c>
       <c r="B1118" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C1118" s="1">
         <v>45442</v>
@@ -49347,7 +49340,7 @@
         <v>13</v>
       </c>
       <c r="B1119" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C1119" s="1">
         <v>45938</v>
@@ -49429,7 +49422,7 @@
         <v>142</v>
       </c>
       <c r="B1121" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C1121" s="1">
         <v>45692</v>
@@ -49470,7 +49463,7 @@
         <v>104</v>
       </c>
       <c r="B1122" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C1122" s="1">
         <v>45426</v>
@@ -49511,7 +49504,7 @@
         <v>43</v>
       </c>
       <c r="B1123" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="C1123" s="1">
         <v>46004</v>
@@ -49552,7 +49545,7 @@
         <v>84</v>
       </c>
       <c r="B1124" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="C1124" s="1">
         <v>45986</v>
@@ -49593,7 +49586,7 @@
         <v>55</v>
       </c>
       <c r="B1125" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="C1125" s="1">
         <v>45412</v>
@@ -49634,7 +49627,7 @@
         <v>32</v>
       </c>
       <c r="B1126" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C1126" s="1">
         <v>45538</v>
@@ -49675,7 +49668,7 @@
         <v>60</v>
       </c>
       <c r="B1127" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="C1127" s="1">
         <v>45573</v>
@@ -49716,7 +49709,7 @@
         <v>71</v>
       </c>
       <c r="B1128" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C1128" s="1">
         <v>45892</v>
@@ -49757,7 +49750,7 @@
         <v>104</v>
       </c>
       <c r="B1129" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C1129" s="1">
         <v>45952</v>
@@ -49798,7 +49791,7 @@
         <v>55</v>
       </c>
       <c r="B1130" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C1130" s="1">
         <v>46009</v>
@@ -49839,7 +49832,7 @@
         <v>79</v>
       </c>
       <c r="B1131" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C1131" s="1">
         <v>45966</v>
@@ -49880,7 +49873,7 @@
         <v>79</v>
       </c>
       <c r="B1132" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C1132" s="1">
         <v>45423</v>
@@ -49921,7 +49914,7 @@
         <v>37</v>
       </c>
       <c r="B1133" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C1133" s="1">
         <v>45810</v>
@@ -49962,7 +49955,7 @@
         <v>26</v>
       </c>
       <c r="B1134" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="C1134" s="1">
         <v>45823</v>
@@ -50003,7 +49996,7 @@
         <v>63</v>
       </c>
       <c r="B1135" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C1135" s="1">
         <v>45970</v>
@@ -50044,7 +50037,7 @@
         <v>63</v>
       </c>
       <c r="B1136" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C1136" s="1">
         <v>45576</v>
@@ -50085,7 +50078,7 @@
         <v>104</v>
       </c>
       <c r="B1137" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C1137" s="1">
         <v>45377</v>
@@ -50126,7 +50119,7 @@
         <v>63</v>
       </c>
       <c r="B1138" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C1138" s="1">
         <v>45869</v>
@@ -50208,7 +50201,7 @@
         <v>52</v>
       </c>
       <c r="B1140" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C1140" s="1">
         <v>45663</v>
@@ -50249,7 +50242,7 @@
         <v>104</v>
       </c>
       <c r="B1141" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C1141" s="1">
         <v>45418</v>
@@ -50290,7 +50283,7 @@
         <v>84</v>
       </c>
       <c r="B1142" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C1142" s="1">
         <v>45856</v>
@@ -50331,7 +50324,7 @@
         <v>84</v>
       </c>
       <c r="B1143" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C1143" s="1">
         <v>45856</v>
@@ -50372,7 +50365,7 @@
         <v>43</v>
       </c>
       <c r="B1144" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="C1144" s="1">
         <v>45679</v>
@@ -50413,7 +50406,7 @@
         <v>60</v>
       </c>
       <c r="B1145" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="C1145" s="1">
         <v>45741</v>
@@ -50454,7 +50447,7 @@
         <v>26</v>
       </c>
       <c r="B1146" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C1146" s="1">
         <v>45604</v>
@@ -50495,7 +50488,7 @@
         <v>55</v>
       </c>
       <c r="B1147" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="C1147" s="1">
         <v>45378</v>
@@ -50536,7 +50529,7 @@
         <v>142</v>
       </c>
       <c r="B1148" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C1148" s="1">
         <v>45819</v>
@@ -50577,7 +50570,7 @@
         <v>129</v>
       </c>
       <c r="B1149" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="C1149" s="1">
         <v>45645</v>
@@ -50618,7 +50611,7 @@
         <v>71</v>
       </c>
       <c r="B1150" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C1150" s="1">
         <v>45368</v>
@@ -50659,7 +50652,7 @@
         <v>84</v>
       </c>
       <c r="B1151" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C1151" s="1">
         <v>45638</v>
@@ -50700,7 +50693,7 @@
         <v>123</v>
       </c>
       <c r="B1152" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="C1152" s="1">
         <v>45514</v>
@@ -50741,7 +50734,7 @@
         <v>32</v>
       </c>
       <c r="B1153" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C1153" s="1">
         <v>45298</v>
@@ -50782,7 +50775,7 @@
         <v>104</v>
       </c>
       <c r="B1154" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C1154" s="1">
         <v>45301</v>
@@ -50823,7 +50816,7 @@
         <v>79</v>
       </c>
       <c r="B1155" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C1155" s="1">
         <v>45299</v>
@@ -50864,7 +50857,7 @@
         <v>13</v>
       </c>
       <c r="B1156" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C1156" s="1">
         <v>45741</v>
@@ -50905,7 +50898,7 @@
         <v>79</v>
       </c>
       <c r="B1157" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C1157" s="1">
         <v>45583</v>
@@ -50946,7 +50939,7 @@
         <v>142</v>
       </c>
       <c r="B1158" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C1158" s="1">
         <v>45413</v>
@@ -50987,7 +50980,7 @@
         <v>104</v>
       </c>
       <c r="B1159" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C1159" s="1">
         <v>45404</v>
@@ -51028,7 +51021,7 @@
         <v>32</v>
       </c>
       <c r="B1160" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C1160" s="1">
         <v>45731</v>
@@ -51069,7 +51062,7 @@
         <v>71</v>
       </c>
       <c r="B1161" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C1161" s="1">
         <v>45815</v>
@@ -51110,7 +51103,7 @@
         <v>63</v>
       </c>
       <c r="B1162" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="C1162" s="1">
         <v>46015</v>
@@ -51151,7 +51144,7 @@
         <v>71</v>
       </c>
       <c r="B1163" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C1163" s="1">
         <v>45427</v>
@@ -51192,7 +51185,7 @@
         <v>37</v>
       </c>
       <c r="B1164" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="C1164" s="1">
         <v>45681</v>
@@ -51233,7 +51226,7 @@
         <v>129</v>
       </c>
       <c r="B1165" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C1165" s="1">
         <v>45603</v>
@@ -51274,7 +51267,7 @@
         <v>32</v>
       </c>
       <c r="B1166" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C1166" s="1">
         <v>45333</v>
@@ -51315,7 +51308,7 @@
         <v>79</v>
       </c>
       <c r="B1167" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C1167" s="1">
         <v>45481</v>
@@ -51356,7 +51349,7 @@
         <v>43</v>
       </c>
       <c r="B1168" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C1168" s="1">
         <v>45661</v>
@@ -51397,7 +51390,7 @@
         <v>104</v>
       </c>
       <c r="B1169" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C1169" s="1">
         <v>45400</v>
@@ -51438,7 +51431,7 @@
         <v>63</v>
       </c>
       <c r="B1170" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C1170" s="1">
         <v>45393</v>
@@ -51479,7 +51472,7 @@
         <v>43</v>
       </c>
       <c r="B1171" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C1171" s="1">
         <v>45422</v>
@@ -51520,7 +51513,7 @@
         <v>84</v>
       </c>
       <c r="B1172" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="C1172" s="1">
         <v>45751</v>
@@ -51561,7 +51554,7 @@
         <v>55</v>
       </c>
       <c r="B1173" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="C1173" s="1">
         <v>46005</v>
@@ -51602,7 +51595,7 @@
         <v>142</v>
       </c>
       <c r="B1174" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C1174" s="1">
         <v>45817</v>
@@ -51643,7 +51636,7 @@
         <v>13</v>
       </c>
       <c r="B1175" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="C1175" s="1">
         <v>45480</v>
@@ -51725,7 +51718,7 @@
         <v>71</v>
       </c>
       <c r="B1177" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C1177" s="1">
         <v>45838</v>
@@ -51766,7 +51759,7 @@
         <v>32</v>
       </c>
       <c r="B1178" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="C1178" s="1">
         <v>45507</v>
@@ -51807,7 +51800,7 @@
         <v>13</v>
       </c>
       <c r="B1179" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C1179" s="1">
         <v>45710</v>
@@ -51848,7 +51841,7 @@
         <v>13</v>
       </c>
       <c r="B1180" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="C1180" s="1">
         <v>45554</v>
@@ -51889,7 +51882,7 @@
         <v>63</v>
       </c>
       <c r="B1181" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="C1181" s="1">
         <v>45517</v>
@@ -51930,7 +51923,7 @@
         <v>60</v>
       </c>
       <c r="B1182" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C1182" s="1">
         <v>45736</v>
@@ -51971,7 +51964,7 @@
         <v>63</v>
       </c>
       <c r="B1183" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C1183" s="1">
         <v>45476</v>
@@ -52053,7 +52046,7 @@
         <v>43</v>
       </c>
       <c r="B1185" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C1185" s="1">
         <v>45909</v>
@@ -52094,7 +52087,7 @@
         <v>43</v>
       </c>
       <c r="B1186" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C1186" s="1">
         <v>45377</v>
@@ -52135,7 +52128,7 @@
         <v>52</v>
       </c>
       <c r="B1187" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C1187" s="1">
         <v>45499</v>
@@ -52217,7 +52210,7 @@
         <v>79</v>
       </c>
       <c r="B1189" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C1189" s="1">
         <v>45595</v>
@@ -52258,7 +52251,7 @@
         <v>129</v>
       </c>
       <c r="B1190" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C1190" s="1">
         <v>45442</v>
@@ -52299,7 +52292,7 @@
         <v>142</v>
       </c>
       <c r="B1191" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C1191" s="1">
         <v>45404</v>
@@ -52340,7 +52333,7 @@
         <v>32</v>
       </c>
       <c r="B1192" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="C1192" s="1">
         <v>45474</v>
@@ -52381,7 +52374,7 @@
         <v>26</v>
       </c>
       <c r="B1193" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C1193" s="1">
         <v>45398</v>
@@ -52422,7 +52415,7 @@
         <v>123</v>
       </c>
       <c r="B1194" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C1194" s="1">
         <v>45963</v>
@@ -52463,7 +52456,7 @@
         <v>37</v>
       </c>
       <c r="B1195" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C1195" s="1">
         <v>45883</v>
@@ -52545,7 +52538,7 @@
         <v>104</v>
       </c>
       <c r="B1197" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C1197" s="1">
         <v>45854</v>
@@ -52627,7 +52620,7 @@
         <v>142</v>
       </c>
       <c r="B1199" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C1199" s="1">
         <v>45404</v>
@@ -52668,7 +52661,7 @@
         <v>129</v>
       </c>
       <c r="B1200" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C1200" s="1">
         <v>45507</v>

--- a/data/retail_dataset_cleaned.xlsx
+++ b/data/retail_dataset_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\retail_data_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21A3CC1-7ED1-4AAA-8F6A-4C4EEDEEC741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AABEB4-6833-49D8-A8D9-90EE28E6E0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,10 +34,10 @@
     <t>region</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>City</t>
+    <t>state</t>
+  </si>
+  <si>
+    <t>city</t>
   </si>
   <si>
     <t>product</t>

--- a/data/retail_dataset_cleaned.xlsx
+++ b/data/retail_dataset_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\retail_data_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AABEB4-6833-49D8-A8D9-90EE28E6E0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B3463DE-B6C0-4C7D-BA96-6B700483B520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
